--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E109298A-9EEE-4A91-980C-DFE85C8CFA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9622F22-647E-4700-ACE6-53EDB916FE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t xml:space="preserve">I need to have better control over my emotions. </t>
+  </si>
+  <si>
+    <t>I have to leave procrastination and should focus on study more.</t>
   </si>
 </sst>
 </file>
@@ -1880,31 +1883,54 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="str">
-        <f>IF(B23&lt;&gt;"",COUNT($B$6:B23),"")</f>
-        <v/>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="10" t="str">
+    <row r="23" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="11">
+        <v>18</v>
+      </c>
+      <c r="B23" s="8">
+        <v>46269</v>
+      </c>
+      <c r="C23" s="9">
+        <v>330</v>
+      </c>
+      <c r="D23" s="9">
+        <v>30</v>
+      </c>
+      <c r="E23" s="9">
+        <v>50</v>
+      </c>
+      <c r="F23" s="9">
+        <v>35</v>
+      </c>
+      <c r="G23" s="9">
+        <v>350</v>
+      </c>
+      <c r="H23" s="9">
+        <v>7</v>
+      </c>
+      <c r="I23" s="9">
+        <v>79</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K23" s="10" t="str">
+        <v>874</v>
+      </c>
+      <c r="K23" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="12"/>
+        <v>566</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9622F22-647E-4700-ACE6-53EDB916FE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FCB173-B15D-49FF-8DF6-25E521F5C910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>I have to leave procrastination and should focus on study more.</t>
+  </si>
+  <si>
+    <t>Wasted my whole day doing Nothing. Need to prepare for ca.</t>
   </si>
 </sst>
 </file>
@@ -1932,31 +1935,54 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="str">
-        <f>IF(B24&lt;&gt;"",COUNT($B$6:B24),"")</f>
-        <v/>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="10" t="str">
+    <row r="24" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>19</v>
+      </c>
+      <c r="B24" s="8">
+        <v>46270</v>
+      </c>
+      <c r="C24" s="9">
+        <v>480</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <v>10</v>
+      </c>
+      <c r="F24" s="9">
+        <v>20</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9">
+        <v>180</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K24" s="10" t="str">
+        <v>690</v>
+      </c>
+      <c r="K24" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="12"/>
+        <v>750</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O24" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FCB173-B15D-49FF-8DF6-25E521F5C910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38B18FF-3A93-4CED-A212-276ECC7ADB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Wasted my whole day doing Nothing. Need to prepare for ca.</t>
+  </si>
+  <si>
+    <t>This will be the last day of wasting my time. From now on study.</t>
   </si>
 </sst>
 </file>
@@ -1984,31 +1987,54 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="str">
-        <f>IF(B25&lt;&gt;"",COUNT($B$6:B25),"")</f>
-        <v/>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="10" t="str">
+    <row r="25" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="11">
+        <v>20</v>
+      </c>
+      <c r="B25" s="8">
+        <v>46271</v>
+      </c>
+      <c r="C25" s="9">
+        <v>450</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
+        <v>20</v>
+      </c>
+      <c r="F25" s="9">
+        <v>30</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0</v>
+      </c>
+      <c r="I25" s="9">
+        <v>120</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K25" s="10" t="str">
+        <v>620</v>
+      </c>
+      <c r="K25" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="12"/>
+        <v>820</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="O25" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38B18FF-3A93-4CED-A212-276ECC7ADB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8745C2-933A-4D47-BA6F-05CE553C2C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>This will be the last day of wasting my time. From now on study.</t>
+  </si>
+  <si>
+    <t>Others are doing so much and here I am doing nothing but that will change.</t>
   </si>
 </sst>
 </file>
@@ -2036,31 +2039,54 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="str">
-        <f>IF(B26&lt;&gt;"",COUNT($B$6:B26),"")</f>
-        <v/>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="10" t="str">
+    <row r="26" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="11">
+        <v>21</v>
+      </c>
+      <c r="B26" s="8">
+        <v>46272</v>
+      </c>
+      <c r="C26" s="9">
+        <v>330</v>
+      </c>
+      <c r="D26" s="9">
+        <v>20</v>
+      </c>
+      <c r="E26" s="9">
+        <v>40</v>
+      </c>
+      <c r="F26" s="9">
+        <v>40</v>
+      </c>
+      <c r="G26" s="9">
+        <v>300</v>
+      </c>
+      <c r="H26" s="9">
+        <v>5</v>
+      </c>
+      <c r="I26" s="9">
+        <v>80</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K26" s="10" t="str">
+        <v>810</v>
+      </c>
+      <c r="K26" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="12"/>
+        <v>630</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8745C2-933A-4D47-BA6F-05CE553C2C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0ED43A-6319-4008-B380-6F8756E222A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Others are doing so much and here I am doing nothing but that will change.</t>
+  </si>
+  <si>
+    <t>I couldn't perform well in my communication presentation.</t>
   </si>
 </sst>
 </file>
@@ -2088,31 +2091,54 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="str">
-        <f>IF(B27&lt;&gt;"",COUNT($B$6:B27),"")</f>
-        <v/>
-      </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="10" t="str">
+    <row r="27" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="11">
+        <v>22</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46273</v>
+      </c>
+      <c r="C27" s="9">
+        <v>360</v>
+      </c>
+      <c r="D27" s="9">
+        <v>30</v>
+      </c>
+      <c r="E27" s="9">
+        <v>50</v>
+      </c>
+      <c r="F27" s="9">
+        <v>50</v>
+      </c>
+      <c r="G27" s="9">
+        <v>300</v>
+      </c>
+      <c r="H27" s="9">
+        <v>5</v>
+      </c>
+      <c r="I27" s="9">
+        <v>240</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K27" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="K27" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="12"/>
+        <v>410</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0ED43A-6319-4008-B380-6F8756E222A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83FBACE-F662-4C18-A331-73BC66073161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>I couldn't perform well in my communication presentation.</t>
+  </si>
+  <si>
+    <t>I think I did good in my dbms CA.</t>
   </si>
 </sst>
 </file>
@@ -2141,30 +2144,53 @@
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="str">
-        <f>IF(B28&lt;&gt;"",COUNT($B$6:B28),"")</f>
-        <v/>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="10" t="str">
+      <c r="A28" s="11">
+        <v>23</v>
+      </c>
+      <c r="B28" s="8">
+        <v>46274</v>
+      </c>
+      <c r="C28" s="9">
+        <v>350</v>
+      </c>
+      <c r="D28" s="9">
+        <v>20</v>
+      </c>
+      <c r="E28" s="9">
+        <v>40</v>
+      </c>
+      <c r="F28" s="9">
+        <v>60</v>
+      </c>
+      <c r="G28" s="9">
+        <v>300</v>
+      </c>
+      <c r="H28" s="9">
+        <v>5</v>
+      </c>
+      <c r="I28" s="9">
+        <v>60</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K28" s="10" t="str">
+        <v>830</v>
+      </c>
+      <c r="K28" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="12"/>
+        <v>610</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83FBACE-F662-4C18-A331-73BC66073161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0526D0C7-AEB9-482E-8A0F-29CDF8DDA031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>I think I did good in my dbms CA.</t>
+  </si>
+  <si>
+    <t>Today was fresher's day. I realized I am not a fan of these type of things.</t>
   </si>
 </sst>
 </file>
@@ -2192,31 +2195,54 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="str">
-        <f>IF(B29&lt;&gt;"",COUNT($B$6:B29),"")</f>
-        <v/>
-      </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="10" t="str">
+    <row r="29" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="11">
+        <v>24</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46275</v>
+      </c>
+      <c r="C29" s="9">
+        <v>380</v>
+      </c>
+      <c r="D29" s="9">
+        <v>30</v>
+      </c>
+      <c r="E29" s="9">
+        <v>80</v>
+      </c>
+      <c r="F29" s="9">
+        <v>10</v>
+      </c>
+      <c r="G29" s="9">
+        <v>100</v>
+      </c>
+      <c r="H29" s="9">
+        <v>2</v>
+      </c>
+      <c r="I29" s="9">
+        <v>15</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K29" s="10" t="str">
+        <v>615</v>
+      </c>
+      <c r="K29" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="12"/>
+        <v>825</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0526D0C7-AEB9-482E-8A0F-29CDF8DDA031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E71E61F-9094-4637-B104-5F22AA237119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>Today was fresher's day. I realized I am not a fan of these type of things.</t>
+  </si>
+  <si>
+    <t>Need to prepare for Analytical Skills upcoming CA exams.</t>
   </si>
 </sst>
 </file>
@@ -2244,31 +2247,54 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="str">
-        <f>IF(B30&lt;&gt;"",COUNT($B$6:B30),"")</f>
-        <v/>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="10" t="str">
+    <row r="30" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="11">
+        <v>25</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46276</v>
+      </c>
+      <c r="C30" s="9">
+        <v>410</v>
+      </c>
+      <c r="D30" s="9">
+        <v>20</v>
+      </c>
+      <c r="E30" s="9">
+        <v>40</v>
+      </c>
+      <c r="F30" s="9">
+        <v>50</v>
+      </c>
+      <c r="G30" s="9">
+        <v>300</v>
+      </c>
+      <c r="H30" s="9">
+        <v>6</v>
+      </c>
+      <c r="I30" s="9">
+        <v>60</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K30" s="10" t="str">
+        <v>880</v>
+      </c>
+      <c r="K30" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="12"/>
+        <v>560</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E71E61F-9094-4637-B104-5F22AA237119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCFFD0F-074F-4DBD-A392-1E031C43AAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>Need to prepare for Analytical Skills upcoming CA exams.</t>
+  </si>
+  <si>
+    <t>Sometimes all you need is just a break from everything.</t>
   </si>
 </sst>
 </file>
@@ -2296,31 +2299,54 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="str">
-        <f>IF(B31&lt;&gt;"",COUNT($B$6:B31),"")</f>
-        <v/>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="10" t="str">
+    <row r="31" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="11">
+        <v>26</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46277</v>
+      </c>
+      <c r="C31" s="9">
+        <v>450</v>
+      </c>
+      <c r="D31" s="9">
+        <v>10</v>
+      </c>
+      <c r="E31" s="9">
+        <v>15</v>
+      </c>
+      <c r="F31" s="9">
+        <v>30</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>0</v>
+      </c>
+      <c r="I31" s="9">
+        <v>240</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K31" s="10" t="str">
+        <v>745</v>
+      </c>
+      <c r="K31" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="12"/>
+        <v>695</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N31" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCFFD0F-074F-4DBD-A392-1E031C43AAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4C5DEE-1864-42C1-BF90-83EF645A90F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>Sometimes all you need is just a break from everything.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I did nothing productive. </t>
   </si>
 </sst>
 </file>
@@ -2349,30 +2352,53 @@
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="str">
-        <f>IF(B32&lt;&gt;"",COUNT($B$6:B32),"")</f>
-        <v/>
-      </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="10" t="str">
+      <c r="A32" s="11">
+        <v>27</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46278</v>
+      </c>
+      <c r="C32" s="9">
+        <v>300</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <v>20</v>
+      </c>
+      <c r="F32" s="9">
+        <v>50</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9">
+        <v>300</v>
+      </c>
+      <c r="J32" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K32" s="10" t="str">
+        <v>670</v>
+      </c>
+      <c r="K32" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="12"/>
+        <v>770</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N32" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O32" s="12" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4C5DEE-1864-42C1-BF90-83EF645A90F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210904A1-D523-428D-925B-D00BCF1A12E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,18 @@
   </si>
   <si>
     <t xml:space="preserve">Today I did nothing productive. </t>
+  </si>
+  <si>
+    <t>Today I gave mars test. I need to better in python.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Today I went with my friend. Being with them makes me happy.</t>
   </si>
 </sst>
 </file>
@@ -2400,63 +2412,106 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="str">
-        <f>IF(B33&lt;&gt;"",COUNT($B$6:B33),"")</f>
-        <v/>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="10" t="str">
+    <row r="33" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="11">
+        <v>28</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46279</v>
+      </c>
+      <c r="C33" s="9">
+        <v>420</v>
+      </c>
+      <c r="D33" s="9">
+        <v>15</v>
+      </c>
+      <c r="E33" s="9">
+        <v>40</v>
+      </c>
+      <c r="F33" s="9">
+        <v>60</v>
+      </c>
+      <c r="G33" s="9">
+        <v>200</v>
+      </c>
+      <c r="H33" s="9">
+        <v>4</v>
+      </c>
+      <c r="I33" s="9">
+        <v>200</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K33" s="10" t="str">
+        <v>935</v>
+      </c>
+      <c r="K33" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="12"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="str">
-        <f>IF(B34&lt;&gt;"",COUNT($B$6:B34),"")</f>
-        <v/>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="10" t="str">
+        <v>505</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O33" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="11">
+        <v>29</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46280</v>
+      </c>
+      <c r="C34" s="9">
+        <v>330</v>
+      </c>
+      <c r="D34" s="9">
+        <v>10</v>
+      </c>
+      <c r="E34" s="9">
+        <v>20</v>
+      </c>
+      <c r="F34" s="9">
+        <v>40</v>
+      </c>
+      <c r="G34" s="9">
+        <v>250</v>
+      </c>
+      <c r="H34" s="9">
+        <v>5</v>
+      </c>
+      <c r="I34" s="9">
+        <v>150</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K34" s="10" t="str">
+        <v>800</v>
+      </c>
+      <c r="K34" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="12"/>
+        <v>640</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O34" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="str">
-        <f>IF(B35&lt;&gt;"",COUNT($B$6:B35),"")</f>
-        <v/>
-      </c>
+      <c r="A35" s="11"/>
       <c r="B35" s="8"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210904A1-D523-428D-925B-D00BCF1A12E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CA8BED-D707-4F53-9BE9-B82844DBFC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,19 +304,22 @@
     <t>Sometimes all you need is just a break from everything.</t>
   </si>
   <si>
-    <t xml:space="preserve">Today I did nothing productive. </t>
-  </si>
-  <si>
-    <t>Today I gave mars test. I need to better in python.</t>
-  </si>
-  <si>
     <t>Excellent</t>
   </si>
   <si>
     <t>Very Satisfied</t>
   </si>
   <si>
-    <t>Today I went with my friend. Being with them makes me happy.</t>
+    <t>Today I gave mars test. I need to do better in python.</t>
+  </si>
+  <si>
+    <t>Today I did nothing productive and just wasted my day.</t>
+  </si>
+  <si>
+    <t>I should have better control on my emotions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytical Skills test date has been out. </t>
   </si>
 </sst>
 </file>
@@ -2363,7 +2366,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>27</v>
       </c>
@@ -2409,10 +2412,10 @@
         <v>51</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <v>28</v>
       </c>
@@ -2449,10 +2452,10 @@
         <v>505</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N33" s="11" t="s">
         <v>51</v>
@@ -2507,31 +2510,57 @@
         <v>51</v>
       </c>
       <c r="O34" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="11">
+        <v>30</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46281</v>
+      </c>
+      <c r="C35" s="9">
+        <v>510</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9">
+        <v>60</v>
+      </c>
+      <c r="F35" s="9">
+        <v>30</v>
+      </c>
+      <c r="G35" s="9">
+        <v>250</v>
+      </c>
+      <c r="H35" s="9">
+        <v>5</v>
+      </c>
+      <c r="I35" s="9">
         <v>90</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="10" t="str">
+      <c r="J35" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K35" s="10" t="str">
+        <v>940</v>
+      </c>
+      <c r="K35" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="12"/>
+        <v>500</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O35" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CA8BED-D707-4F53-9BE9-B82844DBFC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9E1A50-F0B4-4C2C-B619-C110EF447C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t xml:space="preserve">Analytical Skills test date has been out. </t>
+  </si>
+  <si>
+    <t>Feeling stressed I don't know how I would be able to do better.</t>
   </si>
 </sst>
 </file>
@@ -2562,31 +2565,54 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="str">
-        <f>IF(B36&lt;&gt;"",COUNT($B$6:B36),"")</f>
-        <v/>
-      </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="10" t="str">
+    <row r="36" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="11">
+        <v>31</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46282</v>
+      </c>
+      <c r="C36" s="9">
+        <v>290</v>
+      </c>
+      <c r="D36" s="9">
+        <v>10</v>
+      </c>
+      <c r="E36" s="9">
+        <v>45</v>
+      </c>
+      <c r="F36" s="9">
+        <v>30</v>
+      </c>
+      <c r="G36" s="9">
+        <v>300</v>
+      </c>
+      <c r="H36" s="9">
+        <v>6</v>
+      </c>
+      <c r="I36" s="9">
+        <v>60</v>
+      </c>
+      <c r="J36" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K36" s="10" t="str">
+        <v>735</v>
+      </c>
+      <c r="K36" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="12"/>
+        <v>705</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N36" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O36" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9E1A50-F0B4-4C2C-B619-C110EF447C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35AD2FD-EC17-40A8-8F85-495063DEA434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>Feeling stressed I don't know how I would be able to do better.</t>
+  </si>
+  <si>
+    <t>Solving Analytical Problems for two period is very exhausting.</t>
   </si>
 </sst>
 </file>
@@ -2614,37 +2617,57 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="str">
-        <f>IF(B37&lt;&gt;"",COUNT($B$6:B37),"")</f>
-        <v/>
-      </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="10" t="str">
+    <row r="37" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="11">
+        <v>32</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46283</v>
+      </c>
+      <c r="C37" s="9">
+        <v>350</v>
+      </c>
+      <c r="D37" s="9">
+        <v>15</v>
+      </c>
+      <c r="E37" s="9">
+        <v>40</v>
+      </c>
+      <c r="F37" s="9">
+        <v>45</v>
+      </c>
+      <c r="G37" s="9">
+        <v>350</v>
+      </c>
+      <c r="H37" s="9">
+        <v>7</v>
+      </c>
+      <c r="I37" s="9">
+        <v>90</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K37" s="10" t="str">
+        <v>890</v>
+      </c>
+      <c r="K37" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="12"/>
+        <v>550</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N37" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="O37" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="str">
-        <f>IF(B38&lt;&gt;"",COUNT($B$6:B38),"")</f>
-        <v/>
-      </c>
+      <c r="A38" s="11"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35AD2FD-EC17-40A8-8F85-495063DEA434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA59C740-1C09-4EB7-B8B0-630678AF74F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>Solving Analytical Problems for two period is very exhausting.</t>
+  </si>
+  <si>
+    <t>Why do LPU held CA's exams online if they can't manage to do that properly. They have ruined my whole day.</t>
   </si>
 </sst>
 </file>
@@ -2666,28 +2669,54 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="10" t="str">
+    <row r="38" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="11">
+        <v>33</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46284</v>
+      </c>
+      <c r="C38" s="9">
+        <v>240</v>
+      </c>
+      <c r="D38" s="9">
+        <v>10</v>
+      </c>
+      <c r="E38" s="9">
+        <v>20</v>
+      </c>
+      <c r="F38" s="9">
+        <v>10</v>
+      </c>
+      <c r="G38" s="9">
+        <v>60</v>
+      </c>
+      <c r="H38" s="9">
+        <v>1</v>
+      </c>
+      <c r="I38" s="9">
+        <v>360</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K38" s="10" t="str">
+        <v>700</v>
+      </c>
+      <c r="K38" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="12"/>
+        <v>740</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="N38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O38" s="12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="str">

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716FEE19-41EB-4402-ACD2-093282DEAA7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FF66F9-BD7E-4B69-8968-8D629ACB22A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -202,9 +202,6 @@
     <t>P164-NN1:MCA/D1P2635</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
@@ -330,6 +327,27 @@
   <si>
     <t>I really needed this Sunday. This week was so overwhelming.</t>
   </si>
+  <si>
+    <t>Today is the first date of filling my excel routine data.</t>
+  </si>
+  <si>
+    <t>Attending 7 classes is so exhausting.</t>
+  </si>
+  <si>
+    <t>Having no classes helps me more in my studies.</t>
+  </si>
+  <si>
+    <t>On sundays I can do study and rest both.</t>
+  </si>
+  <si>
+    <t>I am  weak in communication need to work on that.</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>I was having a bad day and I even scored badly in one of my CA's</t>
+  </si>
 </sst>
 </file>
 
@@ -338,7 +356,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,6 +430,13 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -433,7 +458,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -456,11 +481,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -486,14 +557,64 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -957,7 +1078,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N406"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -972,74 +1093,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="18">
         <v>12612197</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="15"/>
+      <c r="F3" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="19"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1086,1700 +1207,1844 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="14">
+        <v>46247</v>
+      </c>
+      <c r="B6" s="15">
+        <v>450</v>
+      </c>
+      <c r="C6" s="15">
+        <v>20</v>
+      </c>
+      <c r="D6" s="15">
+        <v>30</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15">
+        <v>300</v>
+      </c>
+      <c r="G6" s="15">
+        <v>6</v>
+      </c>
+      <c r="H6" s="15">
+        <v>240</v>
+      </c>
+      <c r="I6" s="16">
+        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <v>1040</v>
+      </c>
+      <c r="J6" s="16">
+        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <v>400</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="14">
+        <v>46248</v>
+      </c>
+      <c r="B7" s="15">
+        <v>360</v>
+      </c>
+      <c r="C7" s="15">
+        <v>15</v>
+      </c>
+      <c r="D7" s="15">
+        <v>20</v>
+      </c>
+      <c r="E7" s="15">
+        <v>25</v>
+      </c>
+      <c r="F7" s="15">
+        <v>350</v>
+      </c>
+      <c r="G7" s="15">
+        <v>7</v>
+      </c>
+      <c r="H7" s="15">
+        <v>180</v>
+      </c>
+      <c r="I7" s="16">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J7" s="16">
+        <f t="shared" si="1"/>
+        <v>490</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="14">
+        <v>46249</v>
+      </c>
+      <c r="B8" s="15">
+        <v>510</v>
+      </c>
+      <c r="C8" s="15">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
+        <v>40</v>
+      </c>
+      <c r="E8" s="15">
+        <v>60</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0</v>
+      </c>
+      <c r="H8" s="15">
+        <v>150</v>
+      </c>
+      <c r="I8" s="16">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J8" s="16">
+        <f t="shared" si="1"/>
+        <v>680</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="14">
+        <v>46250</v>
+      </c>
+      <c r="B9" s="15">
+        <v>450</v>
+      </c>
+      <c r="C9" s="15">
+        <v>10</v>
+      </c>
+      <c r="D9" s="15">
+        <v>35</v>
+      </c>
+      <c r="E9" s="15">
+        <v>45</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15">
+        <v>0</v>
+      </c>
+      <c r="H9" s="15">
+        <v>90</v>
+      </c>
+      <c r="I9" s="16">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="J9" s="16">
+        <f t="shared" si="1"/>
+        <v>810</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="14">
+        <v>46251</v>
+      </c>
+      <c r="B10" s="15">
+        <v>380</v>
+      </c>
+      <c r="C10" s="15">
+        <v>30</v>
+      </c>
+      <c r="D10" s="15">
+        <v>20</v>
+      </c>
+      <c r="E10" s="15">
+        <v>40</v>
+      </c>
+      <c r="F10" s="15">
+        <v>200</v>
+      </c>
+      <c r="G10" s="15">
+        <v>4</v>
+      </c>
+      <c r="H10" s="15">
+        <v>210</v>
+      </c>
+      <c r="I10" s="16">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J10" s="16">
+        <f t="shared" si="1"/>
+        <v>560</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
         <v>46252</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B11" s="15">
         <v>320</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C11" s="15">
         <v>5</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D11" s="15">
         <v>28</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E11" s="15">
         <v>17</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F11" s="15">
         <v>300</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G11" s="15">
         <v>6</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H11" s="15">
         <v>45</v>
       </c>
-      <c r="I6" s="10">
-        <f t="shared" ref="I6:I14" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+      <c r="I11" s="16">
+        <f t="shared" si="0"/>
         <v>715</v>
       </c>
-      <c r="J6" s="10">
-        <f t="shared" ref="J6:J14" si="1">IF(I6="","",1440-I6)</f>
+      <c r="J11" s="16">
+        <f t="shared" si="1"/>
         <v>725</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="M11" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="M6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+    </row>
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
         <v>46253</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B12" s="15">
         <v>390</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C12" s="15">
         <v>18</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D12" s="15">
         <v>25</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E12" s="15">
         <v>70</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F12" s="15">
         <v>350</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G12" s="15">
         <v>7</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H12" s="15">
         <v>60</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I12" s="16">
         <f t="shared" si="0"/>
         <v>913</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J12" s="16">
         <f t="shared" si="1"/>
         <v>527</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K12" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+    </row>
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
         <v>46254</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B13" s="15">
         <v>370</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C13" s="15">
         <v>45</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D13" s="15">
         <v>40</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E13" s="15">
         <v>55</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F13" s="15">
         <v>150</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G13" s="15">
         <v>3</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H13" s="15">
         <v>55</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I13" s="16">
         <f t="shared" si="0"/>
         <v>715</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J13" s="16">
         <f t="shared" si="1"/>
         <v>725</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K13" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="M13" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="14">
         <v>46255</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B14" s="15">
         <v>440</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C14" s="15">
         <v>15</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D14" s="15">
         <v>70</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E14" s="15">
         <v>95</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F14" s="15">
         <v>0</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G14" s="15">
         <v>0</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H14" s="15">
         <v>120</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I14" s="16">
         <f t="shared" si="0"/>
         <v>740</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J14" s="16">
         <f t="shared" si="1"/>
         <v>700</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K14" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="N14" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="14">
         <v>46256</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B15" s="15">
         <v>510</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C15" s="15">
         <v>0</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D15" s="15">
         <v>35</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E15" s="15">
         <v>30</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F15" s="15">
         <v>0</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G15" s="15">
         <v>0</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H15" s="15">
         <v>155</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I15" s="16">
         <f t="shared" si="0"/>
         <v>730</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J15" s="16">
         <f t="shared" si="1"/>
         <v>710</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K15" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M10" s="11" t="s">
+      <c r="L15" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="N15" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="14">
         <v>46257</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B16" s="15">
         <v>540</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C16" s="15">
         <v>20</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D16" s="15">
         <v>80</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E16" s="15">
         <v>100</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F16" s="15">
         <v>0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G16" s="15">
         <v>0</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H16" s="15">
         <v>90</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I16" s="16">
         <f t="shared" si="0"/>
         <v>830</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J16" s="16">
         <f t="shared" si="1"/>
         <v>610</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K16" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L16" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M16" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="N11" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+    </row>
+    <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="14">
         <v>46258</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B17" s="15">
         <v>370</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C17" s="15">
         <v>10</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D17" s="15">
         <v>20</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E17" s="15">
         <v>60</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F17" s="15">
         <v>200</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G17" s="15">
         <v>4</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H17" s="15">
         <v>80</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I17" s="16">
         <f t="shared" si="0"/>
         <v>740</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J17" s="16">
         <f t="shared" si="1"/>
         <v>700</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K17" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L17" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M17" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="N17" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="14">
         <v>46259</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B18" s="15">
         <v>360</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C18" s="15">
         <v>20</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D18" s="15">
         <v>40</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E18" s="15">
         <v>50</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F18" s="15">
         <v>250</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G18" s="15">
         <v>5</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H18" s="15">
         <v>90</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I18" s="16">
         <f t="shared" si="0"/>
         <v>810</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J18" s="16">
         <f t="shared" si="1"/>
         <v>630</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K18" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L18" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M18" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="N18" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="14">
         <v>46260</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B19" s="15">
         <v>330</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C19" s="15">
         <v>30</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D19" s="15">
         <v>50</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E19" s="15">
         <v>120</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F19" s="15">
         <v>250</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G19" s="15">
         <v>5</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H19" s="15">
         <v>10</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I19" s="16">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J19" s="16">
         <f t="shared" si="1"/>
         <v>650</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K19" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="14">
+        <v>46261</v>
+      </c>
+      <c r="B20" s="15">
+        <v>500</v>
+      </c>
+      <c r="C20" s="15">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
+        <v>30</v>
+      </c>
+      <c r="E20" s="15">
+        <v>120</v>
+      </c>
+      <c r="F20" s="15">
+        <v>300</v>
+      </c>
+      <c r="G20" s="15">
+        <v>6</v>
+      </c>
+      <c r="H20" s="15">
+        <v>50</v>
+      </c>
+      <c r="I20" s="16">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="J20" s="16">
+        <f t="shared" si="1"/>
+        <v>420</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="M20" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="14">
+        <v>46262</v>
+      </c>
+      <c r="B21" s="15">
+        <v>345</v>
+      </c>
+      <c r="C21" s="15">
+        <v>25</v>
+      </c>
+      <c r="D21" s="15">
+        <v>45</v>
+      </c>
+      <c r="E21" s="15">
+        <v>65</v>
+      </c>
+      <c r="F21" s="15">
+        <v>200</v>
+      </c>
+      <c r="G21" s="15">
+        <v>4</v>
+      </c>
+      <c r="H21" s="15">
+        <v>30</v>
+      </c>
+      <c r="I21" s="16">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J21" s="16">
+        <f t="shared" si="1"/>
+        <v>730</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="14">
+        <v>46263</v>
+      </c>
+      <c r="B22" s="15">
+        <v>480</v>
+      </c>
+      <c r="C22" s="15">
+        <v>15</v>
+      </c>
+      <c r="D22" s="15">
+        <v>40</v>
+      </c>
+      <c r="E22" s="15">
         <v>50</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="F22" s="15">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15">
+        <v>0</v>
+      </c>
+      <c r="H22" s="15">
+        <v>100</v>
+      </c>
+      <c r="I22" s="16">
+        <f t="shared" si="0"/>
+        <v>685</v>
+      </c>
+      <c r="J22" s="16">
+        <f t="shared" si="1"/>
+        <v>755</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="N14" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
-        <v>46261</v>
-      </c>
-      <c r="B15" s="9">
+      <c r="M22" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="14">
+        <v>46264</v>
+      </c>
+      <c r="B23" s="15">
+        <v>360</v>
+      </c>
+      <c r="C23" s="15">
+        <v>10</v>
+      </c>
+      <c r="D23" s="15">
+        <v>30</v>
+      </c>
+      <c r="E23" s="15">
+        <v>40</v>
+      </c>
+      <c r="F23" s="15">
+        <v>0</v>
+      </c>
+      <c r="G23" s="15">
+        <v>0</v>
+      </c>
+      <c r="H23" s="15">
+        <v>120</v>
+      </c>
+      <c r="I23" s="16">
+        <f t="shared" si="0"/>
+        <v>560</v>
+      </c>
+      <c r="J23" s="16">
+        <f t="shared" si="1"/>
+        <v>880</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="14">
+        <v>46265</v>
+      </c>
+      <c r="B24" s="15">
+        <v>420</v>
+      </c>
+      <c r="C24" s="15">
+        <v>20</v>
+      </c>
+      <c r="D24" s="15">
+        <v>25</v>
+      </c>
+      <c r="E24" s="15">
+        <v>55</v>
+      </c>
+      <c r="F24" s="15">
+        <v>200</v>
+      </c>
+      <c r="G24" s="15">
+        <v>4</v>
+      </c>
+      <c r="H24" s="15">
+        <v>45</v>
+      </c>
+      <c r="I24" s="16">
+        <f t="shared" si="0"/>
+        <v>765</v>
+      </c>
+      <c r="J24" s="16">
+        <f t="shared" si="1"/>
+        <v>675</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="14">
+        <v>46266</v>
+      </c>
+      <c r="B25" s="15">
+        <v>375</v>
+      </c>
+      <c r="C25" s="15">
+        <v>10</v>
+      </c>
+      <c r="D25" s="15">
+        <v>20</v>
+      </c>
+      <c r="E25" s="15">
+        <v>120</v>
+      </c>
+      <c r="F25" s="15">
+        <v>200</v>
+      </c>
+      <c r="G25" s="15">
+        <v>4</v>
+      </c>
+      <c r="H25" s="15">
+        <v>200</v>
+      </c>
+      <c r="I25" s="16">
+        <f t="shared" si="0"/>
+        <v>925</v>
+      </c>
+      <c r="J25" s="16">
+        <f t="shared" si="1"/>
+        <v>515</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="14">
+        <v>46267</v>
+      </c>
+      <c r="B26" s="15">
+        <v>390</v>
+      </c>
+      <c r="C26" s="15">
+        <v>15</v>
+      </c>
+      <c r="D26" s="15">
+        <v>40</v>
+      </c>
+      <c r="E26" s="15">
+        <v>100</v>
+      </c>
+      <c r="F26" s="15">
+        <v>250</v>
+      </c>
+      <c r="G26" s="15">
+        <v>5</v>
+      </c>
+      <c r="H26" s="15">
+        <v>40</v>
+      </c>
+      <c r="I26" s="16">
+        <f t="shared" si="0"/>
+        <v>835</v>
+      </c>
+      <c r="J26" s="16">
+        <f t="shared" si="1"/>
+        <v>605</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M26" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="14">
+        <v>46268</v>
+      </c>
+      <c r="B27" s="15">
+        <v>420</v>
+      </c>
+      <c r="C27" s="15">
+        <v>25</v>
+      </c>
+      <c r="D27" s="15">
+        <v>35</v>
+      </c>
+      <c r="E27" s="15">
+        <v>45</v>
+      </c>
+      <c r="F27" s="15">
+        <v>360</v>
+      </c>
+      <c r="G27" s="15">
+        <v>6</v>
+      </c>
+      <c r="H27" s="15">
+        <v>90</v>
+      </c>
+      <c r="I27" s="16">
+        <f t="shared" si="0"/>
+        <v>975</v>
+      </c>
+      <c r="J27" s="16">
+        <f t="shared" si="1"/>
+        <v>465</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="L27" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M27" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="14">
+        <v>46269</v>
+      </c>
+      <c r="B28" s="15">
+        <v>330</v>
+      </c>
+      <c r="C28" s="15">
+        <v>30</v>
+      </c>
+      <c r="D28" s="15">
+        <v>50</v>
+      </c>
+      <c r="E28" s="15">
+        <v>35</v>
+      </c>
+      <c r="F28" s="15">
+        <v>350</v>
+      </c>
+      <c r="G28" s="15">
+        <v>7</v>
+      </c>
+      <c r="H28" s="15">
+        <v>79</v>
+      </c>
+      <c r="I28" s="16">
+        <f t="shared" si="0"/>
+        <v>874</v>
+      </c>
+      <c r="J28" s="16">
+        <f t="shared" si="1"/>
+        <v>566</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M28" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="14">
+        <v>46270</v>
+      </c>
+      <c r="B29" s="15">
+        <v>480</v>
+      </c>
+      <c r="C29" s="15">
+        <v>0</v>
+      </c>
+      <c r="D29" s="15">
+        <v>10</v>
+      </c>
+      <c r="E29" s="15">
+        <v>20</v>
+      </c>
+      <c r="F29" s="15">
+        <v>0</v>
+      </c>
+      <c r="G29" s="15">
+        <v>0</v>
+      </c>
+      <c r="H29" s="15">
+        <v>180</v>
+      </c>
+      <c r="I29" s="16">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J29" s="16">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M29" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="14">
+        <v>46271</v>
+      </c>
+      <c r="B30" s="15">
+        <v>450</v>
+      </c>
+      <c r="C30" s="15">
+        <v>0</v>
+      </c>
+      <c r="D30" s="15">
+        <v>20</v>
+      </c>
+      <c r="E30" s="15">
+        <v>30</v>
+      </c>
+      <c r="F30" s="15">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15">
+        <v>0</v>
+      </c>
+      <c r="H30" s="15">
+        <v>120</v>
+      </c>
+      <c r="I30" s="16">
+        <f t="shared" si="0"/>
+        <v>620</v>
+      </c>
+      <c r="J30" s="16">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M30" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="14">
+        <v>46272</v>
+      </c>
+      <c r="B31" s="15">
+        <v>330</v>
+      </c>
+      <c r="C31" s="15">
+        <v>20</v>
+      </c>
+      <c r="D31" s="15">
+        <v>40</v>
+      </c>
+      <c r="E31" s="15">
+        <v>40</v>
+      </c>
+      <c r="F31" s="15">
+        <v>250</v>
+      </c>
+      <c r="G31" s="15">
+        <v>5</v>
+      </c>
+      <c r="H31" s="15">
+        <v>80</v>
+      </c>
+      <c r="I31" s="16">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J31" s="16">
+        <f t="shared" si="1"/>
+        <v>680</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="L31" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="14">
+        <v>46273</v>
+      </c>
+      <c r="B32" s="15">
+        <v>360</v>
+      </c>
+      <c r="C32" s="15">
+        <v>30</v>
+      </c>
+      <c r="D32" s="15">
+        <v>50</v>
+      </c>
+      <c r="E32" s="15">
+        <v>50</v>
+      </c>
+      <c r="F32" s="15">
+        <v>250</v>
+      </c>
+      <c r="G32" s="15">
+        <v>5</v>
+      </c>
+      <c r="H32" s="15">
+        <v>240</v>
+      </c>
+      <c r="I32" s="16">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="J32" s="16">
+        <f t="shared" si="1"/>
+        <v>460</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M32" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="14">
+        <v>46274</v>
+      </c>
+      <c r="B33" s="15">
+        <v>350</v>
+      </c>
+      <c r="C33" s="15">
+        <v>20</v>
+      </c>
+      <c r="D33" s="15">
+        <v>40</v>
+      </c>
+      <c r="E33" s="15">
+        <v>60</v>
+      </c>
+      <c r="F33" s="15">
+        <v>250</v>
+      </c>
+      <c r="G33" s="15">
+        <v>5</v>
+      </c>
+      <c r="H33" s="15">
+        <v>60</v>
+      </c>
+      <c r="I33" s="16">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J33" s="16">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="14">
+        <v>46275</v>
+      </c>
+      <c r="B34" s="15">
+        <v>380</v>
+      </c>
+      <c r="C34" s="15">
+        <v>30</v>
+      </c>
+      <c r="D34" s="15">
+        <v>80</v>
+      </c>
+      <c r="E34" s="15">
+        <v>10</v>
+      </c>
+      <c r="F34" s="15">
+        <v>100</v>
+      </c>
+      <c r="G34" s="15">
+        <v>2</v>
+      </c>
+      <c r="H34" s="15">
+        <v>15</v>
+      </c>
+      <c r="I34" s="16">
+        <f t="shared" si="0"/>
+        <v>615</v>
+      </c>
+      <c r="J34" s="16">
+        <f t="shared" si="1"/>
+        <v>825</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M34" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="14">
+        <v>46276</v>
+      </c>
+      <c r="B35" s="15">
+        <v>410</v>
+      </c>
+      <c r="C35" s="15">
+        <v>20</v>
+      </c>
+      <c r="D35" s="15">
+        <v>40</v>
+      </c>
+      <c r="E35" s="15">
+        <v>50</v>
+      </c>
+      <c r="F35" s="15">
+        <v>300</v>
+      </c>
+      <c r="G35" s="15">
+        <v>6</v>
+      </c>
+      <c r="H35" s="15">
+        <v>60</v>
+      </c>
+      <c r="I35" s="16">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J35" s="16">
+        <f t="shared" si="1"/>
+        <v>560</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="14">
+        <v>46277</v>
+      </c>
+      <c r="B36" s="15">
+        <v>450</v>
+      </c>
+      <c r="C36" s="15">
+        <v>10</v>
+      </c>
+      <c r="D36" s="15">
+        <v>15</v>
+      </c>
+      <c r="E36" s="15">
+        <v>30</v>
+      </c>
+      <c r="F36" s="15">
+        <v>0</v>
+      </c>
+      <c r="G36" s="15">
+        <v>0</v>
+      </c>
+      <c r="H36" s="15">
+        <v>240</v>
+      </c>
+      <c r="I36" s="16">
+        <f t="shared" si="0"/>
+        <v>745</v>
+      </c>
+      <c r="J36" s="16">
+        <f t="shared" si="1"/>
+        <v>695</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="14">
+        <v>46278</v>
+      </c>
+      <c r="B37" s="15">
+        <v>300</v>
+      </c>
+      <c r="C37" s="15">
+        <v>0</v>
+      </c>
+      <c r="D37" s="15">
+        <v>20</v>
+      </c>
+      <c r="E37" s="15">
+        <v>50</v>
+      </c>
+      <c r="F37" s="15">
+        <v>0</v>
+      </c>
+      <c r="G37" s="15">
+        <v>0</v>
+      </c>
+      <c r="H37" s="15">
+        <v>300</v>
+      </c>
+      <c r="I37" s="16">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J37" s="16">
+        <f t="shared" si="1"/>
+        <v>770</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="14">
+        <v>46279</v>
+      </c>
+      <c r="B38" s="15">
+        <v>420</v>
+      </c>
+      <c r="C38" s="15">
+        <v>15</v>
+      </c>
+      <c r="D38" s="15">
+        <v>40</v>
+      </c>
+      <c r="E38" s="15">
+        <v>60</v>
+      </c>
+      <c r="F38" s="15">
+        <v>200</v>
+      </c>
+      <c r="G38" s="15">
+        <v>4</v>
+      </c>
+      <c r="H38" s="15">
+        <v>200</v>
+      </c>
+      <c r="I38" s="16">
+        <f t="shared" si="0"/>
+        <v>935</v>
+      </c>
+      <c r="J38" s="16">
+        <f t="shared" si="1"/>
+        <v>505</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L38" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="M38" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="14">
+        <v>46280</v>
+      </c>
+      <c r="B39" s="15">
+        <v>330</v>
+      </c>
+      <c r="C39" s="15">
+        <v>10</v>
+      </c>
+      <c r="D39" s="15">
+        <v>20</v>
+      </c>
+      <c r="E39" s="15">
+        <v>40</v>
+      </c>
+      <c r="F39" s="15">
+        <v>250</v>
+      </c>
+      <c r="G39" s="15">
+        <v>5</v>
+      </c>
+      <c r="H39" s="15">
+        <v>150</v>
+      </c>
+      <c r="I39" s="16">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J39" s="16">
+        <f t="shared" si="1"/>
+        <v>640</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L39" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M39" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="14">
+        <v>46281</v>
+      </c>
+      <c r="B40" s="15">
+        <v>510</v>
+      </c>
+      <c r="C40" s="15">
+        <v>0</v>
+      </c>
+      <c r="D40" s="15">
+        <v>60</v>
+      </c>
+      <c r="E40" s="15">
+        <v>30</v>
+      </c>
+      <c r="F40" s="15">
+        <v>250</v>
+      </c>
+      <c r="G40" s="15">
+        <v>5</v>
+      </c>
+      <c r="H40" s="15">
+        <v>90</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="0"/>
+        <v>940</v>
+      </c>
+      <c r="J40" s="16">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="C15" s="9">
+      <c r="K40" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M40" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="14">
+        <v>46282</v>
+      </c>
+      <c r="B41" s="15">
+        <v>290</v>
+      </c>
+      <c r="C41" s="15">
+        <v>10</v>
+      </c>
+      <c r="D41" s="15">
+        <v>45</v>
+      </c>
+      <c r="E41" s="15">
+        <v>30</v>
+      </c>
+      <c r="F41" s="15">
+        <v>300</v>
+      </c>
+      <c r="G41" s="15">
+        <v>6</v>
+      </c>
+      <c r="H41" s="15">
+        <v>60</v>
+      </c>
+      <c r="I41" s="16">
+        <f t="shared" si="0"/>
+        <v>735</v>
+      </c>
+      <c r="J41" s="16">
+        <f t="shared" si="1"/>
+        <v>705</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M41" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="14">
+        <v>46283</v>
+      </c>
+      <c r="B42" s="15">
+        <v>350</v>
+      </c>
+      <c r="C42" s="15">
+        <v>15</v>
+      </c>
+      <c r="D42" s="15">
+        <v>40</v>
+      </c>
+      <c r="E42" s="15">
+        <v>45</v>
+      </c>
+      <c r="F42" s="15">
+        <v>350</v>
+      </c>
+      <c r="G42" s="15">
+        <v>7</v>
+      </c>
+      <c r="H42" s="15">
+        <v>90</v>
+      </c>
+      <c r="I42" s="16">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J42" s="16">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L42" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A43" s="14">
+        <v>46284</v>
+      </c>
+      <c r="B43" s="15">
+        <v>240</v>
+      </c>
+      <c r="C43" s="15">
+        <v>10</v>
+      </c>
+      <c r="D43" s="15">
         <v>20</v>
       </c>
-      <c r="D15" s="9">
+      <c r="E43" s="15">
+        <v>10</v>
+      </c>
+      <c r="F43" s="15">
+        <v>60</v>
+      </c>
+      <c r="G43" s="15">
+        <v>1</v>
+      </c>
+      <c r="H43" s="15">
+        <v>360</v>
+      </c>
+      <c r="I43" s="16">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J43" s="16">
+        <f t="shared" si="1"/>
+        <v>740</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="L43" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M43" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="14">
+        <v>46285</v>
+      </c>
+      <c r="B44" s="15">
+        <v>410</v>
+      </c>
+      <c r="C44" s="15">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15">
+        <v>70</v>
+      </c>
+      <c r="E44" s="15">
+        <v>50</v>
+      </c>
+      <c r="F44" s="15">
+        <v>0</v>
+      </c>
+      <c r="G44" s="15">
+        <v>0</v>
+      </c>
+      <c r="H44" s="15">
+        <v>410</v>
+      </c>
+      <c r="I44" s="16">
+        <f t="shared" si="0"/>
+        <v>940</v>
+      </c>
+      <c r="J44" s="16">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="M44" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="14">
+        <v>46286</v>
+      </c>
+      <c r="B45" s="15">
+        <v>350</v>
+      </c>
+      <c r="C45" s="15">
         <v>30</v>
       </c>
-      <c r="E15" s="9">
-        <v>120</v>
-      </c>
-      <c r="F15" s="9">
-        <v>300</v>
-      </c>
-      <c r="G15" s="9">
-        <v>6</v>
-      </c>
-      <c r="H15" s="9">
-        <v>50</v>
-      </c>
-      <c r="I15" s="10">
-        <f t="shared" ref="I15:I69" si="2">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
-        <v>1020</v>
-      </c>
-      <c r="J15" s="10">
-        <f t="shared" ref="J15:J69" si="3">IF(I15="","",1440-I15)</f>
-        <v>420</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
-        <v>46262</v>
-      </c>
-      <c r="B16" s="9">
-        <v>345</v>
-      </c>
-      <c r="C16" s="9">
-        <v>25</v>
-      </c>
-      <c r="D16" s="9">
-        <v>45</v>
-      </c>
-      <c r="E16" s="9">
-        <v>65</v>
-      </c>
-      <c r="F16" s="9">
+      <c r="D45" s="15">
+        <v>40</v>
+      </c>
+      <c r="E45" s="15">
+        <v>60</v>
+      </c>
+      <c r="F45" s="15">
         <v>200</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G45" s="15">
         <v>4</v>
       </c>
-      <c r="H16" s="9">
-        <v>30</v>
-      </c>
-      <c r="I16" s="10">
-        <f t="shared" si="2"/>
-        <v>710</v>
-      </c>
-      <c r="J16" s="10">
-        <f t="shared" si="3"/>
-        <v>730</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L16" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M16" s="11" t="s">
+      <c r="H45" s="15">
+        <v>150</v>
+      </c>
+      <c r="I45" s="16">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J45" s="16">
+        <f t="shared" si="1"/>
+        <v>610</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L45" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="N16" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
-        <v>46263</v>
-      </c>
-      <c r="B17" s="9">
-        <v>480</v>
-      </c>
-      <c r="C17" s="9">
-        <v>15</v>
-      </c>
-      <c r="D17" s="9">
-        <v>40</v>
-      </c>
-      <c r="E17" s="9">
-        <v>50</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>100</v>
-      </c>
-      <c r="I17" s="10">
-        <f t="shared" si="2"/>
-        <v>685</v>
-      </c>
-      <c r="J17" s="10">
-        <f t="shared" si="3"/>
-        <v>755</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L17" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N17" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
-        <v>46264</v>
-      </c>
-      <c r="B18" s="9">
-        <v>360</v>
-      </c>
-      <c r="C18" s="9">
-        <v>10</v>
-      </c>
-      <c r="D18" s="9">
-        <v>30</v>
-      </c>
-      <c r="E18" s="9">
-        <v>40</v>
-      </c>
-      <c r="F18" s="9">
-        <v>0</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>120</v>
-      </c>
-      <c r="I18" s="10">
-        <f t="shared" si="2"/>
-        <v>560</v>
-      </c>
-      <c r="J18" s="10">
-        <f t="shared" si="3"/>
-        <v>880</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N18" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
-        <v>46265</v>
-      </c>
-      <c r="B19" s="9">
-        <v>420</v>
-      </c>
-      <c r="C19" s="9">
-        <v>20</v>
-      </c>
-      <c r="D19" s="9">
-        <v>25</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="M45" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="9">
-        <v>200</v>
-      </c>
-      <c r="G19" s="9">
-        <v>4</v>
-      </c>
-      <c r="H19" s="9">
-        <v>45</v>
-      </c>
-      <c r="I19" s="10">
-        <f t="shared" si="2"/>
-        <v>765</v>
-      </c>
-      <c r="J19" s="10">
-        <f t="shared" si="3"/>
-        <v>675</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N19" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
-        <v>46266</v>
-      </c>
-      <c r="B20" s="9">
-        <v>375</v>
-      </c>
-      <c r="C20" s="9">
-        <v>10</v>
-      </c>
-      <c r="D20" s="9">
-        <v>20</v>
-      </c>
-      <c r="E20" s="9">
-        <v>120</v>
-      </c>
-      <c r="F20" s="9">
-        <v>200</v>
-      </c>
-      <c r="G20" s="9">
-        <v>4</v>
-      </c>
-      <c r="H20" s="9">
-        <v>200</v>
-      </c>
-      <c r="I20" s="10">
-        <f t="shared" si="2"/>
-        <v>925</v>
-      </c>
-      <c r="J20" s="10">
-        <f t="shared" si="3"/>
-        <v>515</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N20" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
-        <v>46267</v>
-      </c>
-      <c r="B21" s="9">
-        <v>390</v>
-      </c>
-      <c r="C21" s="9">
-        <v>15</v>
-      </c>
-      <c r="D21" s="9">
-        <v>40</v>
-      </c>
-      <c r="E21" s="9">
-        <v>100</v>
-      </c>
-      <c r="F21" s="9">
-        <v>300</v>
-      </c>
-      <c r="G21" s="9">
-        <v>5</v>
-      </c>
-      <c r="H21" s="9">
-        <v>40</v>
-      </c>
-      <c r="I21" s="10">
-        <f t="shared" si="2"/>
-        <v>885</v>
-      </c>
-      <c r="J21" s="10">
-        <f t="shared" si="3"/>
-        <v>555</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N21" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
-        <v>46268</v>
-      </c>
-      <c r="B22" s="9">
-        <v>420</v>
-      </c>
-      <c r="C22" s="9">
-        <v>25</v>
-      </c>
-      <c r="D22" s="9">
-        <v>35</v>
-      </c>
-      <c r="E22" s="9">
-        <v>45</v>
-      </c>
-      <c r="F22" s="9">
-        <v>360</v>
-      </c>
-      <c r="G22" s="9">
-        <v>6</v>
-      </c>
-      <c r="H22" s="9">
-        <v>90</v>
-      </c>
-      <c r="I22" s="10">
-        <f t="shared" si="2"/>
-        <v>975</v>
-      </c>
-      <c r="J22" s="10">
-        <f t="shared" si="3"/>
-        <v>465</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N22" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
-        <v>46269</v>
-      </c>
-      <c r="B23" s="9">
-        <v>330</v>
-      </c>
-      <c r="C23" s="9">
-        <v>30</v>
-      </c>
-      <c r="D23" s="9">
-        <v>50</v>
-      </c>
-      <c r="E23" s="9">
-        <v>35</v>
-      </c>
-      <c r="F23" s="9">
-        <v>350</v>
-      </c>
-      <c r="G23" s="9">
-        <v>7</v>
-      </c>
-      <c r="H23" s="9">
-        <v>79</v>
-      </c>
-      <c r="I23" s="10">
-        <f t="shared" si="2"/>
-        <v>874</v>
-      </c>
-      <c r="J23" s="10">
-        <f t="shared" si="3"/>
-        <v>566</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
-        <v>46270</v>
-      </c>
-      <c r="B24" s="9">
-        <v>480</v>
-      </c>
-      <c r="C24" s="9">
-        <v>0</v>
-      </c>
-      <c r="D24" s="9">
-        <v>10</v>
-      </c>
-      <c r="E24" s="9">
-        <v>20</v>
-      </c>
-      <c r="F24" s="9">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9">
-        <v>180</v>
-      </c>
-      <c r="I24" s="10">
-        <f t="shared" si="2"/>
-        <v>690</v>
-      </c>
-      <c r="J24" s="10">
-        <f t="shared" si="3"/>
-        <v>750</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N24" s="12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
-        <v>46271</v>
-      </c>
-      <c r="B25" s="9">
-        <v>450</v>
-      </c>
-      <c r="C25" s="9">
-        <v>0</v>
-      </c>
-      <c r="D25" s="9">
-        <v>20</v>
-      </c>
-      <c r="E25" s="9">
-        <v>30</v>
-      </c>
-      <c r="F25" s="9">
-        <v>0</v>
-      </c>
-      <c r="G25" s="9">
-        <v>0</v>
-      </c>
-      <c r="H25" s="9">
-        <v>120</v>
-      </c>
-      <c r="I25" s="10">
-        <f t="shared" si="2"/>
-        <v>620</v>
-      </c>
-      <c r="J25" s="10">
-        <f t="shared" si="3"/>
-        <v>820</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L25" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
-        <v>46272</v>
-      </c>
-      <c r="B26" s="9">
-        <v>330</v>
-      </c>
-      <c r="C26" s="9">
-        <v>20</v>
-      </c>
-      <c r="D26" s="9">
-        <v>40</v>
-      </c>
-      <c r="E26" s="9">
-        <v>40</v>
-      </c>
-      <c r="F26" s="9">
-        <v>300</v>
-      </c>
-      <c r="G26" s="9">
-        <v>5</v>
-      </c>
-      <c r="H26" s="9">
-        <v>80</v>
-      </c>
-      <c r="I26" s="10">
-        <f t="shared" si="2"/>
-        <v>810</v>
-      </c>
-      <c r="J26" s="10">
-        <f t="shared" si="3"/>
-        <v>630</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L26" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
-        <v>46273</v>
-      </c>
-      <c r="B27" s="9">
-        <v>360</v>
-      </c>
-      <c r="C27" s="9">
-        <v>30</v>
-      </c>
-      <c r="D27" s="9">
-        <v>50</v>
-      </c>
-      <c r="E27" s="9">
-        <v>50</v>
-      </c>
-      <c r="F27" s="9">
-        <v>300</v>
-      </c>
-      <c r="G27" s="9">
-        <v>5</v>
-      </c>
-      <c r="H27" s="9">
-        <v>240</v>
-      </c>
-      <c r="I27" s="10">
-        <f t="shared" si="2"/>
-        <v>1030</v>
-      </c>
-      <c r="J27" s="10">
-        <f t="shared" si="3"/>
-        <v>410</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N27" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
-        <v>46274</v>
-      </c>
-      <c r="B28" s="9">
-        <v>350</v>
-      </c>
-      <c r="C28" s="9">
-        <v>20</v>
-      </c>
-      <c r="D28" s="9">
-        <v>40</v>
-      </c>
-      <c r="E28" s="9">
-        <v>60</v>
-      </c>
-      <c r="F28" s="9">
-        <v>300</v>
-      </c>
-      <c r="G28" s="9">
-        <v>5</v>
-      </c>
-      <c r="H28" s="9">
-        <v>60</v>
-      </c>
-      <c r="I28" s="10">
-        <f t="shared" si="2"/>
-        <v>830</v>
-      </c>
-      <c r="J28" s="10">
-        <f t="shared" si="3"/>
-        <v>610</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L28" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
-        <v>46275</v>
-      </c>
-      <c r="B29" s="9">
-        <v>380</v>
-      </c>
-      <c r="C29" s="9">
-        <v>30</v>
-      </c>
-      <c r="D29" s="9">
-        <v>80</v>
-      </c>
-      <c r="E29" s="9">
-        <v>10</v>
-      </c>
-      <c r="F29" s="9">
-        <v>100</v>
-      </c>
-      <c r="G29" s="9">
-        <v>2</v>
-      </c>
-      <c r="H29" s="9">
-        <v>15</v>
-      </c>
-      <c r="I29" s="10">
-        <f t="shared" si="2"/>
-        <v>615</v>
-      </c>
-      <c r="J29" s="10">
-        <f t="shared" si="3"/>
-        <v>825</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
-        <v>46276</v>
-      </c>
-      <c r="B30" s="9">
-        <v>410</v>
-      </c>
-      <c r="C30" s="9">
-        <v>20</v>
-      </c>
-      <c r="D30" s="9">
-        <v>40</v>
-      </c>
-      <c r="E30" s="9">
-        <v>50</v>
-      </c>
-      <c r="F30" s="9">
-        <v>300</v>
-      </c>
-      <c r="G30" s="9">
-        <v>6</v>
-      </c>
-      <c r="H30" s="9">
-        <v>60</v>
-      </c>
-      <c r="I30" s="10">
-        <f t="shared" si="2"/>
-        <v>880</v>
-      </c>
-      <c r="J30" s="10">
-        <f t="shared" si="3"/>
-        <v>560</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L30" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N30" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
-        <v>46277</v>
-      </c>
-      <c r="B31" s="9">
-        <v>450</v>
-      </c>
-      <c r="C31" s="9">
-        <v>10</v>
-      </c>
-      <c r="D31" s="9">
-        <v>15</v>
-      </c>
-      <c r="E31" s="9">
-        <v>30</v>
-      </c>
-      <c r="F31" s="9">
-        <v>0</v>
-      </c>
-      <c r="G31" s="9">
-        <v>0</v>
-      </c>
-      <c r="H31" s="9">
-        <v>240</v>
-      </c>
-      <c r="I31" s="10">
-        <f t="shared" si="2"/>
-        <v>745</v>
-      </c>
-      <c r="J31" s="10">
-        <f t="shared" si="3"/>
-        <v>695</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L31" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N31" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
-        <v>46278</v>
-      </c>
-      <c r="B32" s="9">
-        <v>300</v>
-      </c>
-      <c r="C32" s="9">
-        <v>0</v>
-      </c>
-      <c r="D32" s="9">
-        <v>20</v>
-      </c>
-      <c r="E32" s="9">
-        <v>50</v>
-      </c>
-      <c r="F32" s="9">
-        <v>0</v>
-      </c>
-      <c r="G32" s="9">
-        <v>0</v>
-      </c>
-      <c r="H32" s="9">
-        <v>300</v>
-      </c>
-      <c r="I32" s="10">
-        <f t="shared" si="2"/>
-        <v>670</v>
-      </c>
-      <c r="J32" s="10">
-        <f t="shared" si="3"/>
-        <v>770</v>
-      </c>
-      <c r="K32" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L32" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M32" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N32" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
-        <v>46279</v>
-      </c>
-      <c r="B33" s="9">
-        <v>420</v>
-      </c>
-      <c r="C33" s="9">
-        <v>15</v>
-      </c>
-      <c r="D33" s="9">
-        <v>40</v>
-      </c>
-      <c r="E33" s="9">
-        <v>60</v>
-      </c>
-      <c r="F33" s="9">
-        <v>200</v>
-      </c>
-      <c r="G33" s="9">
-        <v>4</v>
-      </c>
-      <c r="H33" s="9">
-        <v>200</v>
-      </c>
-      <c r="I33" s="10">
-        <f t="shared" si="2"/>
-        <v>935</v>
-      </c>
-      <c r="J33" s="10">
-        <f t="shared" si="3"/>
-        <v>505</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L33" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="M33" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N33" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="8">
-        <v>46280</v>
-      </c>
-      <c r="B34" s="9">
-        <v>330</v>
-      </c>
-      <c r="C34" s="9">
-        <v>10</v>
-      </c>
-      <c r="D34" s="9">
-        <v>20</v>
-      </c>
-      <c r="E34" s="9">
-        <v>40</v>
-      </c>
-      <c r="F34" s="9">
-        <v>250</v>
-      </c>
-      <c r="G34" s="9">
-        <v>5</v>
-      </c>
-      <c r="H34" s="9">
-        <v>150</v>
-      </c>
-      <c r="I34" s="10">
-        <f t="shared" si="2"/>
-        <v>800</v>
-      </c>
-      <c r="J34" s="10">
-        <f t="shared" si="3"/>
-        <v>640</v>
-      </c>
-      <c r="K34" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L34" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M34" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N34" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
-        <v>46281</v>
-      </c>
-      <c r="B35" s="9">
-        <v>510</v>
-      </c>
-      <c r="C35" s="9">
-        <v>0</v>
-      </c>
-      <c r="D35" s="9">
-        <v>60</v>
-      </c>
-      <c r="E35" s="9">
-        <v>30</v>
-      </c>
-      <c r="F35" s="9">
-        <v>250</v>
-      </c>
-      <c r="G35" s="9">
-        <v>5</v>
-      </c>
-      <c r="H35" s="9">
-        <v>90</v>
-      </c>
-      <c r="I35" s="10">
-        <f t="shared" si="2"/>
-        <v>940</v>
-      </c>
-      <c r="J35" s="10">
-        <f t="shared" si="3"/>
-        <v>500</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L35" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M35" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N35" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="8">
-        <v>46282</v>
-      </c>
-      <c r="B36" s="9">
-        <v>290</v>
-      </c>
-      <c r="C36" s="9">
-        <v>10</v>
-      </c>
-      <c r="D36" s="9">
-        <v>45</v>
-      </c>
-      <c r="E36" s="9">
-        <v>30</v>
-      </c>
-      <c r="F36" s="9">
-        <v>300</v>
-      </c>
-      <c r="G36" s="9">
-        <v>6</v>
-      </c>
-      <c r="H36" s="9">
-        <v>60</v>
-      </c>
-      <c r="I36" s="10">
-        <f t="shared" si="2"/>
-        <v>735</v>
-      </c>
-      <c r="J36" s="10">
-        <f t="shared" si="3"/>
-        <v>705</v>
-      </c>
-      <c r="K36" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L36" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M36" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N36" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="8">
-        <v>46283</v>
-      </c>
-      <c r="B37" s="9">
-        <v>350</v>
-      </c>
-      <c r="C37" s="9">
-        <v>15</v>
-      </c>
-      <c r="D37" s="9">
-        <v>40</v>
-      </c>
-      <c r="E37" s="9">
-        <v>45</v>
-      </c>
-      <c r="F37" s="9">
-        <v>350</v>
-      </c>
-      <c r="G37" s="9">
-        <v>7</v>
-      </c>
-      <c r="H37" s="9">
-        <v>90</v>
-      </c>
-      <c r="I37" s="10">
-        <f t="shared" si="2"/>
-        <v>890</v>
-      </c>
-      <c r="J37" s="10">
-        <f t="shared" si="3"/>
-        <v>550</v>
-      </c>
-      <c r="K37" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M37" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N37" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="8">
-        <v>46284</v>
-      </c>
-      <c r="B38" s="9">
-        <v>240</v>
-      </c>
-      <c r="C38" s="9">
-        <v>10</v>
-      </c>
-      <c r="D38" s="9">
-        <v>20</v>
-      </c>
-      <c r="E38" s="9">
-        <v>10</v>
-      </c>
-      <c r="F38" s="9">
-        <v>60</v>
-      </c>
-      <c r="G38" s="9">
-        <v>1</v>
-      </c>
-      <c r="H38" s="9">
-        <v>360</v>
-      </c>
-      <c r="I38" s="10">
-        <f t="shared" si="2"/>
-        <v>700</v>
-      </c>
-      <c r="J38" s="10">
-        <f t="shared" si="3"/>
-        <v>740</v>
-      </c>
-      <c r="K38" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M38" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="N38" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="8">
-        <v>46285</v>
-      </c>
-      <c r="B39" s="9">
-        <v>410</v>
-      </c>
-      <c r="C39" s="9">
-        <v>0</v>
-      </c>
-      <c r="D39" s="9">
-        <v>70</v>
-      </c>
-      <c r="E39" s="9">
-        <v>50</v>
-      </c>
-      <c r="F39" s="9">
-        <v>0</v>
-      </c>
-      <c r="G39" s="9">
-        <v>0</v>
-      </c>
-      <c r="H39" s="9">
-        <v>410</v>
-      </c>
-      <c r="I39" s="10">
-        <f t="shared" si="2"/>
-        <v>940</v>
-      </c>
-      <c r="J39" s="10">
-        <f t="shared" si="3"/>
-        <v>500</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L39" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M39" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N39" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
+      <c r="N45" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
@@ -2791,11 +3056,11 @@
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J46" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K46" s="11"/>
@@ -2813,11 +3078,11 @@
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J47" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K47" s="11"/>
@@ -2835,11 +3100,11 @@
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J48" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K48" s="11"/>
@@ -2857,11 +3122,11 @@
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J49" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K49" s="11"/>
@@ -2879,11 +3144,11 @@
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J50" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K50" s="11"/>
@@ -2901,11 +3166,11 @@
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
       <c r="I51" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J51" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K51" s="11"/>
@@ -2923,11 +3188,11 @@
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
       <c r="I52" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J52" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K52" s="11"/>
@@ -2945,11 +3210,11 @@
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
       <c r="I53" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J53" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K53" s="11"/>
@@ -2967,11 +3232,11 @@
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
       <c r="I54" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J54" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K54" s="11"/>
@@ -2989,11 +3254,11 @@
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
       <c r="I55" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J55" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K55" s="11"/>
@@ -3011,11 +3276,11 @@
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
       <c r="I56" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J56" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K56" s="11"/>
@@ -3033,11 +3298,11 @@
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
       <c r="I57" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J57" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K57" s="11"/>
@@ -3055,11 +3320,11 @@
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
       <c r="I58" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J58" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K58" s="11"/>
@@ -3077,11 +3342,11 @@
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
       <c r="I59" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J59" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K59" s="11"/>
@@ -3099,11 +3364,11 @@
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
       <c r="I60" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J60" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K60" s="11"/>
@@ -3121,11 +3386,11 @@
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
       <c r="I61" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J61" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K61" s="11"/>
@@ -3143,11 +3408,11 @@
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
       <c r="I62" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J62" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K62" s="11"/>
@@ -3165,11 +3430,11 @@
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
       <c r="I63" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J63" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K63" s="11"/>
@@ -3187,11 +3452,11 @@
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
       <c r="I64" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J64" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K64" s="11"/>
@@ -3209,11 +3474,11 @@
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
       <c r="I65" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J65" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K65" s="11"/>
@@ -3231,11 +3496,11 @@
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J66" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K66" s="11"/>
@@ -3253,11 +3518,11 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
       <c r="I67" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J67" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K67" s="11"/>
@@ -3275,11 +3540,11 @@
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
       <c r="I68" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J68" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K68" s="11"/>
@@ -3297,11 +3562,11 @@
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
       <c r="I69" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J69" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K69" s="11"/>
@@ -3319,11 +3584,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3341,11 +3606,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3363,11 +3628,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3385,11 +3650,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3407,11 +3672,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3429,11 +3694,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3451,11 +3716,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3473,11 +3738,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3495,11 +3760,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3517,11 +3782,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3539,11 +3804,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3561,11 +3826,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3583,11 +3848,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3605,11 +3870,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3627,11 +3892,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3649,11 +3914,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3671,11 +3936,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3693,11 +3958,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3715,11 +3980,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3737,11 +4002,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3759,11 +4024,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3781,11 +4046,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3803,11 +4068,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3825,11 +4090,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3847,11 +4112,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3869,11 +4134,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3891,11 +4156,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3913,11 +4178,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3935,11 +4200,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3957,11 +4222,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3979,11 +4244,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -4001,11 +4266,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4023,11 +4288,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4045,11 +4310,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4067,11 +4332,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4089,11 +4354,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4111,11 +4376,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4133,11 +4398,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4155,11 +4420,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4177,11 +4442,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4199,11 +4464,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4221,11 +4486,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4243,11 +4508,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4265,11 +4530,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4287,11 +4552,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4309,11 +4574,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4331,11 +4596,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4353,11 +4618,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4375,11 +4640,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4397,11 +4662,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4419,11 +4684,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4441,11 +4706,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4463,11 +4728,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4485,11 +4750,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4507,11 +4772,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4529,11 +4794,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4551,11 +4816,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4573,11 +4838,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4595,11 +4860,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4617,11 +4882,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4639,11 +4904,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4661,11 +4926,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4683,11 +4948,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4705,11 +4970,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4727,11 +4992,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4749,11 +5014,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4771,11 +5036,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4793,11 +5058,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4815,11 +5080,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4837,11 +5102,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4859,11 +5124,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4881,11 +5146,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4903,11 +5168,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4925,11 +5190,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4947,11 +5212,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4969,11 +5234,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4991,11 +5256,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5013,11 +5278,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5035,11 +5300,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5057,11 +5322,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5079,11 +5344,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5101,11 +5366,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5123,11 +5388,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5145,11 +5410,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5167,11 +5432,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5189,11 +5454,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5211,11 +5476,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5233,11 +5498,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5255,11 +5520,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5277,11 +5542,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5299,11 +5564,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5321,11 +5586,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5343,11 +5608,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5365,11 +5630,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5387,11 +5652,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5409,11 +5674,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5431,11 +5696,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5453,11 +5718,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5475,11 +5740,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5497,11 +5762,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5519,11 +5784,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5541,11 +5806,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5563,11 +5828,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5585,11 +5850,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5607,11 +5872,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5629,11 +5894,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5651,11 +5916,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5673,11 +5938,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5695,11 +5960,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5717,11 +5982,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5739,11 +6004,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5761,11 +6026,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5783,11 +6048,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5805,11 +6070,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5827,11 +6092,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5849,11 +6114,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5871,11 +6136,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5893,11 +6158,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5915,11 +6180,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5937,11 +6202,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5959,11 +6224,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5981,11 +6246,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -6003,11 +6268,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6025,11 +6290,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6047,11 +6312,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6069,11 +6334,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6091,11 +6356,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6113,11 +6378,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6135,11 +6400,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6157,11 +6422,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6179,11 +6444,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6201,11 +6466,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6223,11 +6488,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6245,11 +6510,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6267,11 +6532,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6289,11 +6554,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6311,11 +6576,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6333,11 +6598,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6355,11 +6620,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6377,11 +6642,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6399,11 +6664,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6421,11 +6686,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6443,11 +6708,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6465,11 +6730,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6487,11 +6752,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6509,11 +6774,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6531,11 +6796,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6553,11 +6818,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6575,11 +6840,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6597,11 +6862,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6619,11 +6884,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6641,11 +6906,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6663,11 +6928,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6685,11 +6950,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6707,11 +6972,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6729,11 +6994,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6751,11 +7016,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6773,11 +7038,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6795,11 +7060,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6817,11 +7082,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6839,11 +7104,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6861,11 +7126,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6883,11 +7148,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6905,11 +7170,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6927,11 +7192,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6949,11 +7214,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6971,11 +7236,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6993,11 +7258,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -7015,11 +7280,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7037,11 +7302,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7059,11 +7324,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7081,11 +7346,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7103,11 +7368,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7125,11 +7390,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7147,11 +7412,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7169,11 +7434,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7191,11 +7456,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7213,11 +7478,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7235,11 +7500,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7257,11 +7522,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7279,11 +7544,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7301,11 +7566,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7323,11 +7588,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7345,11 +7610,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7367,11 +7632,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7389,11 +7654,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7411,11 +7676,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7433,11 +7698,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7455,11 +7720,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7477,11 +7742,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7499,11 +7764,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7521,11 +7786,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7543,11 +7808,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7565,11 +7830,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7587,11 +7852,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7609,11 +7874,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7631,11 +7896,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7653,11 +7918,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7675,11 +7940,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7697,11 +7962,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7719,11 +7984,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7741,11 +8006,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7763,11 +8028,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7785,11 +8050,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7807,11 +8072,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7829,11 +8094,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7851,11 +8116,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7873,11 +8138,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7895,11 +8160,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7917,11 +8182,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7939,11 +8204,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7961,11 +8226,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7983,11 +8248,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -8005,11 +8270,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8027,11 +8292,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8049,11 +8314,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8071,11 +8336,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8093,11 +8358,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8115,11 +8380,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8137,11 +8402,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8159,11 +8424,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8181,11 +8446,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8203,11 +8468,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8225,11 +8490,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8247,11 +8512,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8269,11 +8534,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8291,11 +8556,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8313,11 +8578,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8335,11 +8600,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8357,11 +8622,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8379,11 +8644,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8401,11 +8666,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8423,11 +8688,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8445,11 +8710,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8467,11 +8732,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8489,11 +8754,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8511,11 +8776,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8533,11 +8798,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8555,11 +8820,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8577,11 +8842,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8599,11 +8864,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8621,11 +8886,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8643,11 +8908,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8665,11 +8930,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8687,11 +8952,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8709,11 +8974,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8731,11 +8996,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8753,11 +9018,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8775,11 +9040,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8797,11 +9062,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8819,11 +9084,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8841,11 +9106,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8863,11 +9128,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8885,11 +9150,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8907,11 +9172,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8929,11 +9194,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8951,11 +9216,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8973,11 +9238,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8995,11 +9260,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -9017,11 +9282,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9039,11 +9304,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9061,11 +9326,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9083,11 +9348,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9105,11 +9370,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9127,11 +9392,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9149,11 +9414,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9171,11 +9436,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9193,11 +9458,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9215,11 +9480,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9237,11 +9502,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9259,11 +9524,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9281,11 +9546,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9303,11 +9568,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9325,11 +9590,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9347,11 +9612,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9369,11 +9634,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9391,11 +9656,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9413,11 +9678,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9435,11 +9700,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9457,11 +9722,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9479,11 +9744,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9501,11 +9766,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9523,11 +9788,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9545,11 +9810,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9567,11 +9832,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9589,11 +9854,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9611,11 +9876,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9633,11 +9898,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9655,11 +9920,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9677,11 +9942,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9699,11 +9964,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9721,11 +9986,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9743,11 +10008,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9765,11 +10030,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9787,11 +10052,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9809,11 +10074,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9831,11 +10096,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9853,11 +10118,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9875,11 +10140,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9897,11 +10162,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9919,11 +10184,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9941,11 +10206,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9963,11 +10228,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9985,11 +10250,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -10007,11 +10272,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10029,11 +10294,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10051,11 +10316,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10073,11 +10338,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10095,11 +10360,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10117,11 +10382,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10139,11 +10404,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10161,11 +10426,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10183,11 +10448,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10205,11 +10470,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10227,11 +10492,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10249,11 +10514,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10271,11 +10536,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10293,11 +10558,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10315,11 +10580,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10337,11 +10602,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10359,11 +10624,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I406" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J406" si="13">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10381,11 +10646,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10403,11 +10668,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10425,11 +10690,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10447,11 +10712,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10469,11 +10734,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10491,11 +10756,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10513,11 +10778,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10535,11 +10800,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10557,11 +10822,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10579,11 +10844,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10601,17 +10866,127 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K401" s="11"/>
       <c r="L401" s="11"/>
       <c r="M401" s="11"/>
       <c r="N401" s="12"/>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="8"/>
+      <c r="B402" s="9"/>
+      <c r="C402" s="9"/>
+      <c r="D402" s="9"/>
+      <c r="E402" s="9"/>
+      <c r="F402" s="9"/>
+      <c r="G402" s="9"/>
+      <c r="H402" s="9"/>
+      <c r="I402" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="10" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="11"/>
+      <c r="L402" s="11"/>
+      <c r="M402" s="11"/>
+      <c r="N402" s="12"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="8"/>
+      <c r="B403" s="9"/>
+      <c r="C403" s="9"/>
+      <c r="D403" s="9"/>
+      <c r="E403" s="9"/>
+      <c r="F403" s="9"/>
+      <c r="G403" s="9"/>
+      <c r="H403" s="9"/>
+      <c r="I403" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J403" s="10" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K403" s="11"/>
+      <c r="L403" s="11"/>
+      <c r="M403" s="11"/>
+      <c r="N403" s="12"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A404" s="8"/>
+      <c r="B404" s="9"/>
+      <c r="C404" s="9"/>
+      <c r="D404" s="9"/>
+      <c r="E404" s="9"/>
+      <c r="F404" s="9"/>
+      <c r="G404" s="9"/>
+      <c r="H404" s="9"/>
+      <c r="I404" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J404" s="10" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K404" s="11"/>
+      <c r="L404" s="11"/>
+      <c r="M404" s="11"/>
+      <c r="N404" s="12"/>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A405" s="8"/>
+      <c r="B405" s="9"/>
+      <c r="C405" s="9"/>
+      <c r="D405" s="9"/>
+      <c r="E405" s="9"/>
+      <c r="F405" s="9"/>
+      <c r="G405" s="9"/>
+      <c r="H405" s="9"/>
+      <c r="I405" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J405" s="10" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K405" s="11"/>
+      <c r="L405" s="11"/>
+      <c r="M405" s="11"/>
+      <c r="N405" s="12"/>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A406" s="8"/>
+      <c r="B406" s="9"/>
+      <c r="C406" s="9"/>
+      <c r="D406" s="9"/>
+      <c r="E406" s="9"/>
+      <c r="F406" s="9"/>
+      <c r="G406" s="9"/>
+      <c r="H406" s="9"/>
+      <c r="I406" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J406" s="10" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K406" s="11"/>
+      <c r="L406" s="11"/>
+      <c r="M406" s="11"/>
+      <c r="N406" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10622,21 +10997,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J6:J406">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K406" xr:uid="{D3A1D897-986C-4142-AAAD-8374377897F5}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L406" xr:uid="{33650840-AC5E-4F1B-887B-46ED49D1F365}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M406" xr:uid="{A255EE73-BF12-411E-8BD6-059B37DDCA8B}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FF66F9-BD7E-4B69-8968-8D629ACB22A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1CCF60-735B-4513-A234-537012330A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -348,6 +348,9 @@
   <si>
     <t>I was having a bad day and I even scored badly in one of my CA's</t>
   </si>
+  <si>
+    <t>Working on python minor project and researching.</t>
+  </si>
 </sst>
 </file>
 
@@ -557,7 +560,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -570,51 +572,16 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1093,74 +1060,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>53</v>
       </c>
       <c r="C2" s="20"/>
-      <c r="D2" s="19"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="19">
         <v>12612197</v>
       </c>
-      <c r="G2" s="19"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>54</v>
       </c>
       <c r="C3" s="20"/>
-      <c r="D3" s="19"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1207,1866 +1174,1890 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="14">
+      <c r="A6" s="13">
         <v>46247</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>450</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="14">
         <v>20</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="14">
         <v>30</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="14">
         <v>0</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="14">
         <v>300</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="14">
         <v>6</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="14">
         <v>240</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="15">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1040</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="15">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
         <v>400</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="K6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="17" t="s">
+      <c r="L6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="17" t="s">
+      <c r="N6" s="16" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="13">
         <v>46248</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>360</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="14">
         <v>15</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <v>20</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="14">
         <v>25</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>350</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="14">
         <v>7</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="14">
         <v>180</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
         <v>490</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N7" s="16" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
+      <c r="A8" s="13">
         <v>46249</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>510</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <v>0</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <v>40</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="14">
         <v>60</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>0</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="14">
         <v>0</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>150</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
         <v>760</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
         <v>680</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="17" t="s">
+      <c r="L8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="17" t="s">
+      <c r="N8" s="16" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="13">
         <v>46250</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>450</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <v>10</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <v>35</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <v>45</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>0</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="14">
         <v>0</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="14">
         <v>90</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
         <v>630</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
         <v>810</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="K9" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="17" t="s">
+      <c r="L9" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N9" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+      <c r="A10" s="13">
         <v>46251</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>380</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <v>30</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <v>20</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="14">
         <v>40</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>200</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="14">
         <v>4</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="14">
         <v>210</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
         <v>880</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
         <v>560</v>
       </c>
-      <c r="K10" s="17" t="s">
+      <c r="K10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="17" t="s">
+      <c r="L10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N10" s="16" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
+      <c r="A11" s="13">
         <v>46252</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="14">
         <v>320</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="14">
         <v>5</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="14">
         <v>28</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="14">
         <v>17</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <v>300</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="14">
         <v>6</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="14">
         <v>45</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
         <v>715</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
         <v>725</v>
       </c>
-      <c r="K11" s="17" t="s">
+      <c r="K11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L11" s="17" t="s">
+      <c r="L11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="N11" s="16" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="14">
+      <c r="A12" s="13">
         <v>46253</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <v>390</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <v>18</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <v>25</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <v>70</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="14">
         <v>350</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="14">
         <v>7</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="14">
         <v>60</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
         <v>913</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
         <v>527</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="K12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L12" s="17" t="s">
+      <c r="L12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="N12" s="16" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
+      <c r="A13" s="13">
         <v>46254</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="14">
         <v>370</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="14">
         <v>45</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <v>40</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="14">
         <v>55</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="14">
         <v>150</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="14">
         <v>3</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="14">
         <v>55</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
         <v>715</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
         <v>725</v>
       </c>
-      <c r="K13" s="17" t="s">
+      <c r="K13" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L13" s="17" t="s">
+      <c r="L13" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="N13" s="16" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="14">
+      <c r="A14" s="13">
         <v>46255</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <v>440</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <v>15</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <v>70</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <v>95</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="14">
         <v>0</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="14">
         <v>0</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="14">
         <v>120</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
         <v>740</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
         <v>700</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="17" t="s">
+      <c r="L14" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="17" t="s">
+      <c r="M14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="17" t="s">
+      <c r="N14" s="16" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
+      <c r="A15" s="13">
         <v>46256</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="14">
         <v>510</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <v>0</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <v>35</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <v>30</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <v>0</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="14">
         <v>0</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="14">
         <v>155</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
         <v>730</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
         <v>710</v>
       </c>
-      <c r="K15" s="17" t="s">
+      <c r="K15" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="17" t="s">
+      <c r="L15" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M15" s="17" t="s">
+      <c r="M15" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="17" t="s">
+      <c r="N15" s="16" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="14">
+      <c r="A16" s="13">
         <v>46257</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <v>540</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <v>20</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <v>80</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <v>100</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <v>0</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <v>0</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="14">
         <v>90</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
         <v>830</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
         <v>610</v>
       </c>
-      <c r="K16" s="17" t="s">
+      <c r="K16" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L16" s="17" t="s">
+      <c r="L16" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="17" t="s">
+      <c r="M16" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="N16" s="17" t="s">
+      <c r="N16" s="16" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="14">
+      <c r="A17" s="13">
         <v>46258</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <v>370</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
         <v>10</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <v>20</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <v>60</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="14">
         <v>200</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="14">
         <v>4</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="14">
         <v>80</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
         <v>740</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
         <v>700</v>
       </c>
-      <c r="K17" s="17" t="s">
+      <c r="K17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L17" s="17" t="s">
+      <c r="L17" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="17" t="s">
+      <c r="M17" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N17" s="17" t="s">
+      <c r="N17" s="16" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
+      <c r="A18" s="13">
         <v>46259</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <v>360</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <v>20</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <v>40</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="14">
         <v>50</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="14">
         <v>250</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="14">
         <v>5</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="14">
         <v>90</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
         <v>810</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
         <v>630</v>
       </c>
-      <c r="K18" s="17" t="s">
+      <c r="K18" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L18" s="17" t="s">
+      <c r="L18" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M18" s="17" t="s">
+      <c r="M18" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="17" t="s">
+      <c r="N18" s="16" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="14">
+      <c r="A19" s="13">
         <v>46260</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="14">
         <v>330</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="14">
         <v>30</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="14">
         <v>50</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="14">
         <v>120</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="14">
         <v>250</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="14">
         <v>5</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="14">
         <v>10</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
         <v>650</v>
       </c>
-      <c r="K19" s="17" t="s">
+      <c r="K19" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="17" t="s">
+      <c r="L19" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M19" s="17" t="s">
+      <c r="M19" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N19" s="17" t="s">
+      <c r="N19" s="16" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="14">
+      <c r="A20" s="13">
         <v>46261</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="14">
         <v>500</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="14">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="14">
         <v>30</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="14">
         <v>120</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="14">
         <v>300</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="14">
         <v>6</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="14">
         <v>50</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K20" s="17" t="s">
+      <c r="K20" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L20" s="17" t="s">
+      <c r="L20" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M20" s="17" t="s">
+      <c r="M20" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N20" s="17" t="s">
+      <c r="N20" s="16" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="14">
+      <c r="A21" s="13">
         <v>46262</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="14">
         <v>345</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="14">
         <v>25</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="14">
         <v>45</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="14">
         <v>65</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="14">
         <v>200</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="14">
         <v>4</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="14">
         <v>30</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
         <v>710</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
         <v>730</v>
       </c>
-      <c r="K21" s="17" t="s">
+      <c r="K21" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="L21" s="17" t="s">
+      <c r="L21" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M21" s="17" t="s">
+      <c r="M21" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N21" s="17" t="s">
+      <c r="N21" s="16" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="14">
+      <c r="A22" s="13">
         <v>46263</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="14">
         <v>480</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="14">
         <v>15</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="14">
         <v>40</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="14">
         <v>50</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="14">
         <v>0</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="14">
         <v>0</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="14">
         <v>100</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
         <v>685</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
         <v>755</v>
       </c>
-      <c r="K22" s="17" t="s">
+      <c r="K22" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L22" s="17" t="s">
+      <c r="L22" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M22" s="17" t="s">
+      <c r="M22" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N22" s="17" t="s">
+      <c r="N22" s="16" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="14">
+      <c r="A23" s="13">
         <v>46264</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="14">
         <v>360</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="14">
         <v>10</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="14">
         <v>30</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="14">
         <v>40</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="14">
         <v>0</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="14">
         <v>0</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="14">
         <v>120</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
         <v>560</v>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
         <v>880</v>
       </c>
-      <c r="K23" s="17" t="s">
+      <c r="K23" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L23" s="17" t="s">
+      <c r="L23" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M23" s="17" t="s">
+      <c r="M23" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N23" s="17" t="s">
+      <c r="N23" s="16" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="14">
+      <c r="A24" s="13">
         <v>46265</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="14">
         <v>420</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="14">
         <v>20</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="14">
         <v>25</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="14">
         <v>55</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="14">
         <v>200</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="14">
         <v>4</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="14">
         <v>45</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
         <v>765</v>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
         <v>675</v>
       </c>
-      <c r="K24" s="17" t="s">
+      <c r="K24" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L24" s="17" t="s">
+      <c r="L24" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M24" s="17" t="s">
+      <c r="M24" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N24" s="17" t="s">
+      <c r="N24" s="16" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="14">
+      <c r="A25" s="13">
         <v>46266</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="14">
         <v>375</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
         <v>10</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="14">
         <v>20</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="14">
         <v>120</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="14">
         <v>200</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="14">
         <v>4</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="14">
         <v>200</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
         <v>925</v>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
         <v>515</v>
       </c>
-      <c r="K25" s="17" t="s">
+      <c r="K25" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L25" s="17" t="s">
+      <c r="L25" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M25" s="17" t="s">
+      <c r="M25" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N25" s="17" t="s">
+      <c r="N25" s="16" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="14">
+      <c r="A26" s="13">
         <v>46267</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="14">
         <v>390</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
         <v>15</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="14">
         <v>40</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="14">
         <v>100</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="14">
         <v>250</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="14">
         <v>5</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="14">
         <v>40</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
         <v>835</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
         <v>605</v>
       </c>
-      <c r="K26" s="17" t="s">
+      <c r="K26" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L26" s="17" t="s">
+      <c r="L26" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M26" s="17" t="s">
+      <c r="M26" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="17" t="s">
+      <c r="N26" s="16" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="14">
+      <c r="A27" s="13">
         <v>46268</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="14">
         <v>420</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="14">
         <v>25</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
         <v>35</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="14">
         <v>45</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="14">
         <v>360</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="14">
         <v>6</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="14">
         <v>90</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
         <v>975</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
         <v>465</v>
       </c>
-      <c r="K27" s="17" t="s">
+      <c r="K27" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="L27" s="17" t="s">
+      <c r="L27" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M27" s="17" t="s">
+      <c r="M27" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N27" s="17" t="s">
+      <c r="N27" s="16" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="14">
+      <c r="A28" s="13">
         <v>46269</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="14">
         <v>330</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="14">
         <v>30</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="14">
         <v>50</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="14">
         <v>35</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="14">
         <v>350</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="14">
         <v>7</v>
       </c>
-      <c r="H28" s="15">
+      <c r="H28" s="14">
         <v>79</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
         <v>874</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
         <v>566</v>
       </c>
-      <c r="K28" s="17" t="s">
+      <c r="K28" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L28" s="17" t="s">
+      <c r="L28" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M28" s="17" t="s">
+      <c r="M28" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N28" s="17" t="s">
+      <c r="N28" s="16" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="14">
+      <c r="A29" s="13">
         <v>46270</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="14">
         <v>480</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="14">
         <v>0</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="14">
         <v>10</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="14">
         <v>20</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="14">
         <v>0</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="14">
         <v>0</v>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="14">
         <v>180</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
         <v>690</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
         <v>750</v>
       </c>
-      <c r="K29" s="17" t="s">
+      <c r="K29" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L29" s="17" t="s">
+      <c r="L29" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M29" s="17" t="s">
+      <c r="M29" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N29" s="17" t="s">
+      <c r="N29" s="16" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="14">
+      <c r="A30" s="13">
         <v>46271</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="14">
         <v>450</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="14">
         <v>0</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="14">
         <v>20</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="14">
         <v>30</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="14">
         <v>0</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="14">
         <v>0</v>
       </c>
-      <c r="H30" s="15">
+      <c r="H30" s="14">
         <v>120</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
         <v>620</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
         <v>820</v>
       </c>
-      <c r="K30" s="17" t="s">
+      <c r="K30" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L30" s="17" t="s">
+      <c r="L30" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M30" s="17" t="s">
+      <c r="M30" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="N30" s="17" t="s">
+      <c r="N30" s="16" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="14">
+      <c r="A31" s="13">
         <v>46272</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="14">
         <v>330</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="14">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="14">
         <v>40</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="14">
         <v>40</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="14">
         <v>250</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="14">
         <v>5</v>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="14">
         <v>80</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
         <v>760</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
         <v>680</v>
       </c>
-      <c r="K31" s="17" t="s">
+      <c r="K31" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="L31" s="17" t="s">
+      <c r="L31" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M31" s="17" t="s">
+      <c r="M31" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N31" s="17" t="s">
+      <c r="N31" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="14">
+      <c r="A32" s="13">
         <v>46273</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="14">
         <v>360</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="14">
         <v>30</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="14">
         <v>50</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="14">
         <v>50</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="14">
         <v>250</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="14">
         <v>5</v>
       </c>
-      <c r="H32" s="15">
+      <c r="H32" s="14">
         <v>240</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
         <v>980</v>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
         <v>460</v>
       </c>
-      <c r="K32" s="17" t="s">
+      <c r="K32" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L32" s="17" t="s">
+      <c r="L32" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M32" s="17" t="s">
+      <c r="M32" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N32" s="17" t="s">
+      <c r="N32" s="16" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="14">
+      <c r="A33" s="13">
         <v>46274</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="14">
         <v>350</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="14">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="14">
         <v>40</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="14">
         <v>60</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="14">
         <v>250</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="14">
         <v>5</v>
       </c>
-      <c r="H33" s="15">
+      <c r="H33" s="14">
         <v>60</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
         <v>780</v>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
         <v>660</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="K33" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L33" s="17" t="s">
+      <c r="L33" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M33" s="17" t="s">
+      <c r="M33" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="N33" s="17" t="s">
+      <c r="N33" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="14">
+      <c r="A34" s="13">
         <v>46275</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="14">
         <v>380</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="14">
         <v>30</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="14">
         <v>80</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="14">
         <v>10</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="14">
         <v>100</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="14">
         <v>2</v>
       </c>
-      <c r="H34" s="15">
+      <c r="H34" s="14">
         <v>15</v>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
         <v>615</v>
       </c>
-      <c r="J34" s="16">
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
         <v>825</v>
       </c>
-      <c r="K34" s="17" t="s">
+      <c r="K34" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L34" s="17" t="s">
+      <c r="L34" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M34" s="17" t="s">
+      <c r="M34" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N34" s="17" t="s">
+      <c r="N34" s="16" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="14">
+      <c r="A35" s="13">
         <v>46276</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="14">
         <v>410</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="14">
         <v>20</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="14">
         <v>40</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="14">
         <v>50</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="14">
         <v>300</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="14">
         <v>6</v>
       </c>
-      <c r="H35" s="15">
+      <c r="H35" s="14">
         <v>60</v>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
         <v>880</v>
       </c>
-      <c r="J35" s="16">
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
         <v>560</v>
       </c>
-      <c r="K35" s="17" t="s">
+      <c r="K35" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L35" s="17" t="s">
+      <c r="L35" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M35" s="17" t="s">
+      <c r="M35" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N35" s="17" t="s">
+      <c r="N35" s="16" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="14">
+      <c r="A36" s="13">
         <v>46277</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="14">
         <v>450</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="14">
         <v>10</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="14">
         <v>15</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="14">
         <v>30</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="14">
         <v>0</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="14">
         <v>0</v>
       </c>
-      <c r="H36" s="15">
+      <c r="H36" s="14">
         <v>240</v>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
         <v>745</v>
       </c>
-      <c r="J36" s="16">
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
         <v>695</v>
       </c>
-      <c r="K36" s="17" t="s">
+      <c r="K36" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L36" s="17" t="s">
+      <c r="L36" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M36" s="17" t="s">
+      <c r="M36" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="N36" s="17" t="s">
+      <c r="N36" s="16" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="14">
+      <c r="A37" s="13">
         <v>46278</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="14">
         <v>300</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="14">
         <v>0</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="14">
         <v>20</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="14">
         <v>50</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="14">
         <v>0</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="14">
         <v>0</v>
       </c>
-      <c r="H37" s="15">
+      <c r="H37" s="14">
         <v>300</v>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
         <v>670</v>
       </c>
-      <c r="J37" s="16">
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
         <v>770</v>
       </c>
-      <c r="K37" s="17" t="s">
+      <c r="K37" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L37" s="17" t="s">
+      <c r="L37" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M37" s="17" t="s">
+      <c r="M37" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N37" s="17" t="s">
+      <c r="N37" s="16" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="14">
+      <c r="A38" s="13">
         <v>46279</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="14">
         <v>420</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="14">
         <v>15</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="14">
         <v>40</v>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="14">
         <v>60</v>
       </c>
-      <c r="F38" s="15">
+      <c r="F38" s="14">
         <v>200</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="14">
         <v>4</v>
       </c>
-      <c r="H38" s="15">
+      <c r="H38" s="14">
         <v>200</v>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
         <v>935</v>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
         <v>505</v>
       </c>
-      <c r="K38" s="17" t="s">
+      <c r="K38" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="L38" s="17" t="s">
+      <c r="L38" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="M38" s="17" t="s">
+      <c r="M38" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N38" s="17" t="s">
+      <c r="N38" s="16" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="14">
+      <c r="A39" s="13">
         <v>46280</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="14">
         <v>330</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>10</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="14">
         <v>20</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>40</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="14">
         <v>250</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>5</v>
       </c>
-      <c r="H39" s="15">
+      <c r="H39" s="14">
         <v>150</v>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="J39" s="16">
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
         <v>640</v>
       </c>
-      <c r="K39" s="17" t="s">
+      <c r="K39" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L39" s="17" t="s">
+      <c r="L39" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M39" s="17" t="s">
+      <c r="M39" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N39" s="17" t="s">
+      <c r="N39" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="14">
+      <c r="A40" s="13">
         <v>46281</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="14">
         <v>510</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>0</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="14">
         <v>60</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>30</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="14">
         <v>250</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>5</v>
       </c>
-      <c r="H40" s="15">
+      <c r="H40" s="14">
         <v>90</v>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
         <v>940</v>
       </c>
-      <c r="J40" s="16">
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="K40" s="17" t="s">
+      <c r="K40" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L40" s="17" t="s">
+      <c r="L40" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M40" s="17" t="s">
+      <c r="M40" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N40" s="17" t="s">
+      <c r="N40" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="14">
+      <c r="A41" s="13">
         <v>46282</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="14">
         <v>290</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>10</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="14">
         <v>45</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>30</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="14">
         <v>300</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>6</v>
       </c>
-      <c r="H41" s="15">
+      <c r="H41" s="14">
         <v>60</v>
       </c>
-      <c r="I41" s="16">
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
         <v>735</v>
       </c>
-      <c r="J41" s="16">
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
         <v>705</v>
       </c>
-      <c r="K41" s="17" t="s">
+      <c r="K41" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="17" t="s">
+      <c r="L41" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M41" s="17" t="s">
+      <c r="M41" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N41" s="17" t="s">
+      <c r="N41" s="16" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="14">
+      <c r="A42" s="13">
         <v>46283</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="14">
         <v>350</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>15</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="14">
         <v>40</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>45</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="14">
         <v>350</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>7</v>
       </c>
-      <c r="H42" s="15">
+      <c r="H42" s="14">
         <v>90</v>
       </c>
-      <c r="I42" s="16">
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="J42" s="16">
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="K42" s="17" t="s">
+      <c r="K42" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L42" s="17" t="s">
+      <c r="L42" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M42" s="17" t="s">
+      <c r="M42" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N42" s="17" t="s">
+      <c r="N42" s="16" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A43" s="14">
+      <c r="A43" s="13">
         <v>46284</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="14">
         <v>240</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>10</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="14">
         <v>20</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>10</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="14">
         <v>60</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>1</v>
       </c>
-      <c r="H43" s="15">
+      <c r="H43" s="14">
         <v>360</v>
       </c>
-      <c r="I43" s="16">
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
-      <c r="J43" s="16">
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
         <v>740</v>
       </c>
-      <c r="K43" s="17" t="s">
+      <c r="K43" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="L43" s="17" t="s">
+      <c r="L43" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M43" s="17" t="s">
+      <c r="M43" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N43" s="17" t="s">
+      <c r="N43" s="16" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="14">
+      <c r="A44" s="13">
         <v>46285</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="14">
         <v>410</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>0</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="14">
         <v>70</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>50</v>
       </c>
-      <c r="F44" s="15">
+      <c r="F44" s="14">
         <v>0</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>0</v>
       </c>
-      <c r="H44" s="15">
+      <c r="H44" s="14">
         <v>410</v>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
         <v>940</v>
       </c>
-      <c r="J44" s="16">
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="K44" s="17" t="s">
+      <c r="K44" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L44" s="17" t="s">
+      <c r="L44" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M44" s="17" t="s">
+      <c r="M44" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N44" s="17" t="s">
+      <c r="N44" s="16" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="14">
+      <c r="A45" s="13">
         <v>46286</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="14">
         <v>350</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>30</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="14">
         <v>40</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>60</v>
       </c>
-      <c r="F45" s="15">
+      <c r="F45" s="14">
         <v>200</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>4</v>
       </c>
-      <c r="H45" s="15">
+      <c r="H45" s="14">
         <v>150</v>
       </c>
-      <c r="I45" s="16">
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
         <v>830</v>
       </c>
-      <c r="J45" s="16">
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
         <v>610</v>
       </c>
-      <c r="K45" s="17" t="s">
+      <c r="K45" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L45" s="17" t="s">
+      <c r="L45" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M45" s="17" t="s">
+      <c r="M45" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N45" s="17" t="s">
+      <c r="N45" s="16" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
+    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B46" s="9">
+        <v>300</v>
+      </c>
+      <c r="C46" s="9">
+        <v>20</v>
+      </c>
+      <c r="D46" s="9">
+        <v>60</v>
+      </c>
+      <c r="E46" s="9">
+        <v>60</v>
+      </c>
+      <c r="F46" s="9">
+        <v>250</v>
+      </c>
+      <c r="G46" s="9">
+        <v>5</v>
+      </c>
+      <c r="H46" s="9">
+        <v>220</v>
+      </c>
+      <c r="I46" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
+        <v>910</v>
+      </c>
+      <c r="J46" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="12"/>
+        <v>530</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
@@ -10998,7 +10989,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J406">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1CCF60-735B-4513-A234-537012330A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C53195-F6B0-460B-AF56-177190A95A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>Working on python minor project and researching.</t>
+  </si>
+  <si>
+    <t>Fixed some problems occurred during minor project coding.</t>
   </si>
 </sst>
 </file>
@@ -1199,11 +1202,11 @@
         <v>240</v>
       </c>
       <c r="I6" s="15">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I45" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1040</v>
       </c>
       <c r="J6" s="15">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J45" si="1">IF(I6="","",1440-I6)</f>
         <v>400</v>
       </c>
       <c r="K6" s="16" t="s">
@@ -3039,11 +3042,9 @@
         <v>220</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" si="0"/>
         <v>910</v>
       </c>
       <c r="J46" s="10">
-        <f t="shared" si="1"/>
         <v>530</v>
       </c>
       <c r="K46" s="11" t="s">
@@ -3059,27 +3060,51 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B47" s="9">
+        <v>240</v>
+      </c>
+      <c r="C47" s="9">
+        <v>10</v>
+      </c>
+      <c r="D47" s="9">
+        <v>20</v>
+      </c>
+      <c r="E47" s="9">
+        <v>40</v>
+      </c>
+      <c r="F47" s="9">
+        <v>250</v>
+      </c>
+      <c r="G47" s="9">
+        <v>5</v>
+      </c>
+      <c r="H47" s="9">
+        <v>180</v>
+      </c>
+      <c r="I47" s="10">
+        <f t="shared" ref="I47:I69" si="2">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
+        <v>740</v>
+      </c>
+      <c r="J47" s="10">
+        <f t="shared" ref="J47:J69" si="3">IF(I47="","",1440-I47)</f>
+        <v>700</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
@@ -3091,11 +3116,11 @@
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J48" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K48" s="11"/>
@@ -3113,11 +3138,11 @@
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J49" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K49" s="11"/>
@@ -3135,11 +3160,11 @@
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J50" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K50" s="11"/>
@@ -3157,11 +3182,11 @@
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
       <c r="I51" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J51" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K51" s="11"/>
@@ -3179,11 +3204,11 @@
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
       <c r="I52" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J52" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K52" s="11"/>
@@ -3201,11 +3226,11 @@
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
       <c r="I53" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J53" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K53" s="11"/>
@@ -3223,11 +3248,11 @@
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
       <c r="I54" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J54" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K54" s="11"/>
@@ -3245,11 +3270,11 @@
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
       <c r="I55" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J55" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K55" s="11"/>
@@ -3267,11 +3292,11 @@
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
       <c r="I56" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J56" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K56" s="11"/>
@@ -3289,11 +3314,11 @@
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
       <c r="I57" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J57" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K57" s="11"/>
@@ -3311,11 +3336,11 @@
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
       <c r="I58" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J58" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K58" s="11"/>
@@ -3333,11 +3358,11 @@
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
       <c r="I59" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J59" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K59" s="11"/>
@@ -3355,11 +3380,11 @@
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
       <c r="I60" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J60" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K60" s="11"/>
@@ -3377,11 +3402,11 @@
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
       <c r="I61" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J61" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K61" s="11"/>
@@ -3399,11 +3424,11 @@
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
       <c r="I62" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J62" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K62" s="11"/>
@@ -3421,11 +3446,11 @@
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
       <c r="I63" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J63" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K63" s="11"/>
@@ -3443,11 +3468,11 @@
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
       <c r="I64" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J64" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K64" s="11"/>
@@ -3465,11 +3490,11 @@
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
       <c r="I65" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J65" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K65" s="11"/>
@@ -3487,11 +3512,11 @@
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J66" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K66" s="11"/>
@@ -3509,11 +3534,11 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
       <c r="I67" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J67" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K67" s="11"/>
@@ -3531,11 +3556,11 @@
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
       <c r="I68" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J68" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K68" s="11"/>
@@ -3553,11 +3578,11 @@
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
       <c r="I69" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J69" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K69" s="11"/>
@@ -3575,11 +3600,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3597,11 +3622,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3619,11 +3644,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3641,11 +3666,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3663,11 +3688,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3685,11 +3710,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3707,11 +3732,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3729,11 +3754,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3751,11 +3776,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3773,11 +3798,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3795,11 +3820,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3817,11 +3842,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3839,11 +3864,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3861,11 +3886,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3883,11 +3908,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3905,11 +3930,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3927,11 +3952,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3949,11 +3974,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3971,11 +3996,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3993,11 +4018,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -4015,11 +4040,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -4037,11 +4062,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -4059,11 +4084,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -4081,11 +4106,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -4103,11 +4128,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -4125,11 +4150,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -4147,11 +4172,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -4169,11 +4194,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -4191,11 +4216,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -4213,11 +4238,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -4235,11 +4260,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -4257,11 +4282,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4279,11 +4304,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4301,11 +4326,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4323,11 +4348,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4345,11 +4370,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4367,11 +4392,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4389,11 +4414,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4411,11 +4436,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4433,11 +4458,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4455,11 +4480,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4477,11 +4502,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4499,11 +4524,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4521,11 +4546,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4543,11 +4568,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4565,11 +4590,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4587,11 +4612,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4609,11 +4634,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4631,11 +4656,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4653,11 +4678,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4675,11 +4700,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4697,11 +4722,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4719,11 +4744,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4741,11 +4766,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4763,11 +4788,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4785,11 +4810,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4807,11 +4832,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4829,11 +4854,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4851,11 +4876,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4873,11 +4898,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4895,11 +4920,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4917,11 +4942,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4939,11 +4964,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4961,11 +4986,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4983,11 +5008,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -5005,11 +5030,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -5027,11 +5052,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -5049,11 +5074,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -5071,11 +5096,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -5093,11 +5118,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -5115,11 +5140,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -5137,11 +5162,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -5159,11 +5184,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -5181,11 +5206,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -5203,11 +5228,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -5225,11 +5250,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -5247,11 +5272,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5269,11 +5294,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5291,11 +5316,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5313,11 +5338,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5335,11 +5360,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5357,11 +5382,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5379,11 +5404,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5401,11 +5426,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5423,11 +5448,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5445,11 +5470,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5467,11 +5492,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5489,11 +5514,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5511,11 +5536,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5533,11 +5558,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5555,11 +5580,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5577,11 +5602,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5599,11 +5624,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5621,11 +5646,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5643,11 +5668,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5665,11 +5690,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5687,11 +5712,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5709,11 +5734,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5731,11 +5756,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5753,11 +5778,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5775,11 +5800,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5797,11 +5822,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5819,11 +5844,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5841,11 +5866,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5863,11 +5888,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5885,11 +5910,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5907,11 +5932,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5929,11 +5954,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5951,11 +5976,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5973,11 +5998,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5995,11 +6020,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -6017,11 +6042,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -6039,11 +6064,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -6061,11 +6086,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -6083,11 +6108,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -6105,11 +6130,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -6127,11 +6152,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -6149,11 +6174,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -6171,11 +6196,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -6193,11 +6218,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -6215,11 +6240,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -6237,11 +6262,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -6259,11 +6284,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6281,11 +6306,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6303,11 +6328,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6325,11 +6350,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6347,11 +6372,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6369,11 +6394,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6391,11 +6416,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6413,11 +6438,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6435,11 +6460,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6457,11 +6482,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6479,11 +6504,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6501,11 +6526,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6523,11 +6548,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6545,11 +6570,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6567,11 +6592,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6589,11 +6614,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6611,11 +6636,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6633,11 +6658,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6655,11 +6680,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6677,11 +6702,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6699,11 +6724,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6721,11 +6746,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6743,11 +6768,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6765,11 +6790,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6787,11 +6812,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6809,11 +6834,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6831,11 +6856,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6853,11 +6878,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6875,11 +6900,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6897,11 +6922,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6919,11 +6944,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6941,11 +6966,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6963,11 +6988,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6985,11 +7010,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -7007,11 +7032,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -7029,11 +7054,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -7051,11 +7076,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -7073,11 +7098,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -7095,11 +7120,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -7117,11 +7142,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -7139,11 +7164,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -7161,11 +7186,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -7183,11 +7208,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -7205,11 +7230,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -7227,11 +7252,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -7249,11 +7274,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -7271,11 +7296,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7293,11 +7318,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7315,11 +7340,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7337,11 +7362,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7359,11 +7384,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7381,11 +7406,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7403,11 +7428,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7425,11 +7450,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7447,11 +7472,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7469,11 +7494,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7491,11 +7516,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7513,11 +7538,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7535,11 +7560,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7557,11 +7582,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7579,11 +7604,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7601,11 +7626,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7623,11 +7648,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7645,11 +7670,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7667,11 +7692,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7689,11 +7714,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7711,11 +7736,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7733,11 +7758,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7755,11 +7780,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7777,11 +7802,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7799,11 +7824,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7821,11 +7846,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7843,11 +7868,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7865,11 +7890,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7887,11 +7912,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7909,11 +7934,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7931,11 +7956,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7953,11 +7978,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7975,11 +8000,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7997,11 +8022,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -8019,11 +8044,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -8041,11 +8066,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -8063,11 +8088,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -8085,11 +8110,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -8107,11 +8132,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -8129,11 +8154,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -8151,11 +8176,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -8173,11 +8198,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -8195,11 +8220,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -8217,11 +8242,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -8239,11 +8264,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -8261,11 +8286,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8283,11 +8308,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8305,11 +8330,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8327,11 +8352,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8349,11 +8374,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8371,11 +8396,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8393,11 +8418,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8415,11 +8440,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8437,11 +8462,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8459,11 +8484,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8481,11 +8506,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8503,11 +8528,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8525,11 +8550,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8547,11 +8572,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8569,11 +8594,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8591,11 +8616,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8613,11 +8638,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8635,11 +8660,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8657,11 +8682,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8679,11 +8704,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8701,11 +8726,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8723,11 +8748,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8745,11 +8770,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8767,11 +8792,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8789,11 +8814,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8811,11 +8836,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8833,11 +8858,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8855,11 +8880,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8877,11 +8902,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8899,11 +8924,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8921,11 +8946,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8943,11 +8968,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8965,11 +8990,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8987,11 +9012,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -9009,11 +9034,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -9031,11 +9056,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -9053,11 +9078,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -9075,11 +9100,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -9097,11 +9122,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -9119,11 +9144,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -9141,11 +9166,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -9163,11 +9188,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -9185,11 +9210,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -9207,11 +9232,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -9229,11 +9254,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -9251,11 +9276,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -9273,11 +9298,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9295,11 +9320,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9317,11 +9342,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9339,11 +9364,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9361,11 +9386,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9383,11 +9408,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9405,11 +9430,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9427,11 +9452,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9449,11 +9474,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9471,11 +9496,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9493,11 +9518,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9515,11 +9540,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9537,11 +9562,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9559,11 +9584,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9581,11 +9606,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9603,11 +9628,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9625,11 +9650,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9647,11 +9672,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9669,11 +9694,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9691,11 +9716,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9713,11 +9738,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9735,11 +9760,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9757,11 +9782,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9779,11 +9804,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9801,11 +9826,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9823,11 +9848,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9845,11 +9870,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9867,11 +9892,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9889,11 +9914,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9911,11 +9936,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9933,11 +9958,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9955,11 +9980,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9977,11 +10002,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9999,11 +10024,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -10021,11 +10046,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -10043,11 +10068,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -10065,11 +10090,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -10087,11 +10112,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -10109,11 +10134,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -10131,11 +10156,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -10153,11 +10178,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -10175,11 +10200,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -10197,11 +10222,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -10219,11 +10244,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -10241,11 +10266,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -10263,11 +10288,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10285,11 +10310,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10307,11 +10332,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10329,11 +10354,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10351,11 +10376,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10373,11 +10398,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10395,11 +10420,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10417,11 +10442,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10439,11 +10464,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10461,11 +10486,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10483,11 +10508,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10505,11 +10530,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10527,11 +10552,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10549,11 +10574,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10571,11 +10596,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10593,11 +10618,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10615,11 +10640,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I406" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I406" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J406" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J406" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10637,11 +10662,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10659,11 +10684,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10681,11 +10706,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10703,11 +10728,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10725,11 +10750,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10747,11 +10772,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10769,11 +10794,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10791,11 +10816,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10813,11 +10838,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10835,11 +10860,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10857,11 +10882,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="11"/>
@@ -10879,11 +10904,11 @@
       <c r="G402" s="9"/>
       <c r="H402" s="9"/>
       <c r="I402" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J402" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K402" s="11"/>
@@ -10901,11 +10926,11 @@
       <c r="G403" s="9"/>
       <c r="H403" s="9"/>
       <c r="I403" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J403" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K403" s="11"/>
@@ -10923,11 +10948,11 @@
       <c r="G404" s="9"/>
       <c r="H404" s="9"/>
       <c r="I404" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J404" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K404" s="11"/>
@@ -10945,11 +10970,11 @@
       <c r="G405" s="9"/>
       <c r="H405" s="9"/>
       <c r="I405" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J405" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K405" s="11"/>
@@ -10967,11 +10992,11 @@
       <c r="G406" s="9"/>
       <c r="H406" s="9"/>
       <c r="I406" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J406" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K406" s="11"/>

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C53195-F6B0-460B-AF56-177190A95A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC61A4CB-E7A9-477D-B234-FCA27529EA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,21 @@
   </si>
   <si>
     <t>Fixed some problems occurred during minor project coding.</t>
+  </si>
+  <si>
+    <t>Preparing for upcoming english CA exams.</t>
+  </si>
+  <si>
+    <t>Feeling very tired after attendig so many classes.</t>
+  </si>
+  <si>
+    <t>Felling relaxed because of day off from college.</t>
+  </si>
+  <si>
+    <t>Watching videos of our campus getting destroyed was very sad.</t>
+  </si>
+  <si>
+    <t>10 days holidays are announced need to prepare concepts.</t>
   </si>
 </sst>
 </file>
@@ -3106,115 +3121,235 @@
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B48" s="9">
+        <v>320</v>
+      </c>
+      <c r="C48" s="9">
+        <v>15</v>
+      </c>
+      <c r="D48" s="9">
+        <v>40</v>
+      </c>
+      <c r="E48" s="9">
+        <v>30</v>
+      </c>
+      <c r="F48" s="9">
+        <v>300</v>
+      </c>
+      <c r="G48" s="9">
+        <v>6</v>
+      </c>
+      <c r="H48" s="9">
+        <v>200</v>
+      </c>
+      <c r="I48" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
+        <v>905</v>
+      </c>
+      <c r="J48" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10" t="str">
+        <v>535</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B49" s="9">
+        <v>360</v>
+      </c>
+      <c r="C49" s="9">
+        <v>20</v>
+      </c>
+      <c r="D49" s="9">
+        <v>25</v>
+      </c>
+      <c r="E49" s="9">
+        <v>35</v>
+      </c>
+      <c r="F49" s="9">
+        <v>350</v>
+      </c>
+      <c r="G49" s="9">
+        <v>7</v>
+      </c>
+      <c r="H49" s="9">
+        <v>120</v>
+      </c>
+      <c r="I49" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="str">
+        <v>910</v>
+      </c>
+      <c r="J49" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="12"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10" t="str">
+        <v>530</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B50" s="9">
+        <v>450</v>
+      </c>
+      <c r="C50" s="9">
+        <v>30</v>
+      </c>
+      <c r="D50" s="9">
+        <v>60</v>
+      </c>
+      <c r="E50" s="9">
+        <v>60</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>210</v>
+      </c>
+      <c r="I50" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="str">
+        <v>810</v>
+      </c>
+      <c r="J50" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="12"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="10" t="str">
+        <v>630</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B51" s="9">
+        <v>430</v>
+      </c>
+      <c r="C51" s="9">
+        <v>20</v>
+      </c>
+      <c r="D51" s="9">
+        <v>50</v>
+      </c>
+      <c r="E51" s="9">
+        <v>60</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>170</v>
+      </c>
+      <c r="I51" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J51" s="10" t="str">
+        <v>730</v>
+      </c>
+      <c r="J51" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="12"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="10" t="str">
+        <v>710</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B52" s="9">
+        <v>440</v>
+      </c>
+      <c r="C52" s="9">
+        <v>25</v>
+      </c>
+      <c r="D52" s="9">
+        <v>40</v>
+      </c>
+      <c r="E52" s="9">
+        <v>50</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>240</v>
+      </c>
+      <c r="I52" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J52" s="10" t="str">
+        <v>795</v>
+      </c>
+      <c r="J52" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="12"/>
+        <v>645</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC61A4CB-E7A9-477D-B234-FCA27529EA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47538D4-19DA-4207-ADD0-4501E0A4DDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,15 @@
   </si>
   <si>
     <t>10 days holidays are announced need to prepare concepts.</t>
+  </si>
+  <si>
+    <t>Working on DSA Concept Bracket Balancing.</t>
+  </si>
+  <si>
+    <t>Working on DSA Concept Infix to Postfix Conversion.</t>
+  </si>
+  <si>
+    <t>Working on DSA Conecpt Postifix Evalucation.</t>
   </si>
 </sst>
 </file>
@@ -3032,393 +3041,467 @@
       </c>
     </row>
     <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="8">
+      <c r="A46" s="13">
         <v>46287</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="14">
         <v>300</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="14">
         <v>20</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="14">
         <v>60</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="14">
         <v>60</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="14">
         <v>250</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="14">
         <v>5</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="14">
         <v>220</v>
       </c>
-      <c r="I46" s="10">
+      <c r="I46" s="15">
         <v>910</v>
       </c>
-      <c r="J46" s="10">
+      <c r="J46" s="15">
         <v>530</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K46" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L46" s="11" t="s">
+      <c r="L46" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M46" s="11" t="s">
+      <c r="M46" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N46" s="12" t="s">
+      <c r="N46" s="16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="8">
+    <row r="47" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
         <v>46288</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="14">
         <v>240</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="14">
         <v>10</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="14">
         <v>20</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="14">
         <v>40</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="14">
         <v>250</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="14">
         <v>5</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="14">
         <v>180</v>
       </c>
-      <c r="I47" s="10">
+      <c r="I47" s="15">
         <f t="shared" ref="I47:I69" si="2">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
         <v>740</v>
       </c>
-      <c r="J47" s="10">
+      <c r="J47" s="15">
         <f t="shared" ref="J47:J69" si="3">IF(I47="","",1440-I47)</f>
         <v>700</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="K47" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L47" s="11" t="s">
+      <c r="L47" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M47" s="11" t="s">
+      <c r="M47" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N47" s="12" t="s">
+      <c r="N47" s="16" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="8">
+      <c r="A48" s="13">
         <v>46289</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="14">
         <v>320</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="14">
         <v>15</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="14">
         <v>40</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="14">
         <v>30</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="14">
         <v>300</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="14">
         <v>6</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="14">
         <v>200</v>
       </c>
-      <c r="I48" s="10">
+      <c r="I48" s="15">
         <f t="shared" si="2"/>
         <v>905</v>
       </c>
-      <c r="J48" s="10">
+      <c r="J48" s="15">
         <f t="shared" si="3"/>
         <v>535</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K48" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L48" s="11" t="s">
+      <c r="L48" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M48" s="11" t="s">
+      <c r="M48" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N48" s="12" t="s">
+      <c r="N48" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="8">
+      <c r="A49" s="13">
         <v>46290</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="14">
         <v>360</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="14">
         <v>20</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="14">
         <v>25</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="14">
         <v>35</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="14">
         <v>350</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="14">
         <v>7</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="14">
         <v>120</v>
       </c>
-      <c r="I49" s="10">
+      <c r="I49" s="15">
         <f t="shared" si="2"/>
         <v>910</v>
       </c>
-      <c r="J49" s="10">
+      <c r="J49" s="15">
         <f t="shared" si="3"/>
         <v>530</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L49" s="11" t="s">
+      <c r="L49" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M49" s="11" t="s">
+      <c r="M49" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N49" s="12" t="s">
+      <c r="N49" s="16" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="8">
+      <c r="A50" s="13">
         <v>46291</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="14">
         <v>450</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="14">
         <v>30</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="14">
         <v>60</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="14">
         <v>60</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="14">
         <v>0</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="14">
         <v>0</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="14">
         <v>210</v>
       </c>
-      <c r="I50" s="10">
+      <c r="I50" s="15">
         <f t="shared" si="2"/>
         <v>810</v>
       </c>
-      <c r="J50" s="10">
+      <c r="J50" s="15">
         <f t="shared" si="3"/>
         <v>630</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="K50" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L50" s="11" t="s">
+      <c r="L50" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M50" s="11" t="s">
+      <c r="M50" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N50" s="12" t="s">
+      <c r="N50" s="16" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="8">
+    <row r="51" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="13">
         <v>46292</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="14">
         <v>430</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="14">
         <v>20</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="14">
         <v>50</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="14">
         <v>60</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="14">
         <v>0</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="14">
         <v>0</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="14">
         <v>170</v>
       </c>
-      <c r="I51" s="10">
+      <c r="I51" s="15">
         <f t="shared" si="2"/>
         <v>730</v>
       </c>
-      <c r="J51" s="10">
+      <c r="J51" s="15">
         <f t="shared" si="3"/>
         <v>710</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="K51" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="L51" s="11" t="s">
+      <c r="L51" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M51" s="11" t="s">
+      <c r="M51" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N51" s="12" t="s">
+      <c r="N51" s="16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="8">
+    <row r="52" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="13">
         <v>46293</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="14">
         <v>440</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="14">
         <v>25</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="14">
         <v>40</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="14">
         <v>50</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="14">
         <v>0</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="14">
         <v>0</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="14">
         <v>240</v>
       </c>
-      <c r="I52" s="10">
+      <c r="I52" s="15">
         <f t="shared" si="2"/>
         <v>795</v>
       </c>
-      <c r="J52" s="10">
+      <c r="J52" s="15">
         <f t="shared" si="3"/>
         <v>645</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="K52" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L52" s="11" t="s">
+      <c r="L52" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M52" s="11" t="s">
+      <c r="M52" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N52" s="12" t="s">
+      <c r="N52" s="16" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="10" t="str">
+    <row r="53" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B53" s="14">
+        <v>450</v>
+      </c>
+      <c r="C53" s="14">
+        <v>20</v>
+      </c>
+      <c r="D53" s="14">
+        <v>60</v>
+      </c>
+      <c r="E53" s="14">
+        <v>60</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>220</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J53" s="10" t="str">
+        <v>810</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="12"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="10" t="str">
+        <v>630</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B54" s="14">
+        <v>490</v>
+      </c>
+      <c r="C54" s="14">
+        <v>25</v>
+      </c>
+      <c r="D54" s="14">
+        <v>60</v>
+      </c>
+      <c r="E54" s="14">
+        <v>50</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>180</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J54" s="10" t="str">
+        <v>805</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="12"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="10" t="str">
+        <v>635</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N54" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B55" s="14">
+        <v>510</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>50</v>
+      </c>
+      <c r="E55" s="14">
+        <v>40</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>260</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J55" s="10" t="str">
+        <v>860</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="12"/>
+        <v>580</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N55" s="16" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="8"/>
+      <c r="A56" s="8">
+        <v>46297</v>
+      </c>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>

--- a/12612197.xlsx
+++ b/12612197.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Journey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47538D4-19DA-4207-ADD0-4501E0A4DDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172332AC-DC4F-416F-BC19-BA5A64E9AC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="133">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -376,7 +376,64 @@
     <t>Working on DSA Concept Infix to Postfix Conversion.</t>
   </si>
   <si>
-    <t>Working on DSA Conecpt Postifix Evalucation.</t>
+    <t>Today I did well in my networking Exam.</t>
+  </si>
+  <si>
+    <t>I need to focus more on C++ Advace concept. Could have done better in Exam.</t>
+  </si>
+  <si>
+    <t>DBMS Exam was very easy. Need to work hard for final of DBMS.</t>
+  </si>
+  <si>
+    <t>Tomorrow is Analytical Skill exam. It's very tough.</t>
+  </si>
+  <si>
+    <t>I didn't do well on my exam. I should have studied more.</t>
+  </si>
+  <si>
+    <t>I did okay I today's english exam. Will focus on grammer.</t>
+  </si>
+  <si>
+    <t>Today I relaxed and did nothing important.</t>
+  </si>
+  <si>
+    <t>I only got one day break after exam.</t>
+  </si>
+  <si>
+    <t>Enjoyed the Dussehra Mela with my friend.</t>
+  </si>
+  <si>
+    <t>C++ will have Project as CA instread of Exams.</t>
+  </si>
+  <si>
+    <t>Today was our first online class and it went well.</t>
+  </si>
+  <si>
+    <t>Preparing for my upcoming exams.</t>
+  </si>
+  <si>
+    <t>Need to do better in Networking Practicals.</t>
+  </si>
+  <si>
+    <t>Need to prepare DBMS Theory</t>
+  </si>
+  <si>
+    <t>Tried to python oops programming.</t>
+  </si>
+  <si>
+    <t>Today's online class was optional still attended it.</t>
+  </si>
+  <si>
+    <t>From Tomorrow onwards online classes will be held.</t>
+  </si>
+  <si>
+    <t>Need to prepare for my upcoming exams.</t>
+  </si>
+  <si>
+    <t>Working on DSA Conecpt Postifix Evaluation.</t>
+  </si>
+  <si>
+    <t>Concept of postfix and infix evaluation.</t>
   </si>
 </sst>
 </file>
@@ -3495,450 +3552,928 @@
         <v>55</v>
       </c>
       <c r="N55" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B56" s="14">
+        <v>480</v>
+      </c>
+      <c r="C56" s="14">
+        <v>15</v>
+      </c>
+      <c r="D56" s="14">
+        <v>60</v>
+      </c>
+      <c r="E56" s="14">
+        <v>60</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>190</v>
+      </c>
+      <c r="I56" s="15">
+        <f t="shared" si="2"/>
+        <v>805</v>
+      </c>
+      <c r="J56" s="15">
+        <f t="shared" si="3"/>
+        <v>635</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N56" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B57" s="14">
+        <v>470</v>
+      </c>
+      <c r="C57" s="14">
+        <v>20</v>
+      </c>
+      <c r="D57" s="14">
+        <v>50</v>
+      </c>
+      <c r="E57" s="14">
+        <v>80</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>260</v>
+      </c>
+      <c r="I57" s="15">
+        <f t="shared" si="2"/>
+        <v>880</v>
+      </c>
+      <c r="J57" s="15">
+        <f t="shared" si="3"/>
+        <v>560</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B58" s="14">
+        <v>490</v>
+      </c>
+      <c r="C58" s="14">
+        <v>25</v>
+      </c>
+      <c r="D58" s="14">
+        <v>40</v>
+      </c>
+      <c r="E58" s="14">
+        <v>40</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>240</v>
+      </c>
+      <c r="I58" s="15">
+        <f t="shared" si="2"/>
+        <v>835</v>
+      </c>
+      <c r="J58" s="15">
+        <f t="shared" si="3"/>
+        <v>605</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N58" s="16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B59" s="14">
+        <v>420</v>
+      </c>
+      <c r="C59" s="14">
+        <v>20</v>
+      </c>
+      <c r="D59" s="14">
+        <v>30</v>
+      </c>
+      <c r="E59" s="14">
+        <v>30</v>
+      </c>
+      <c r="F59" s="14">
+        <v>200</v>
+      </c>
+      <c r="G59" s="14">
+        <v>4</v>
+      </c>
+      <c r="H59" s="14">
+        <v>180</v>
+      </c>
+      <c r="I59" s="15">
+        <f t="shared" si="2"/>
+        <v>880</v>
+      </c>
+      <c r="J59" s="15">
+        <f t="shared" si="3"/>
+        <v>560</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N59" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B60" s="14">
+        <v>410</v>
+      </c>
+      <c r="C60" s="14">
+        <v>25</v>
+      </c>
+      <c r="D60" s="14">
+        <v>40</v>
+      </c>
+      <c r="E60" s="14">
+        <v>60</v>
+      </c>
+      <c r="F60" s="14">
+        <v>250</v>
+      </c>
+      <c r="G60" s="14">
+        <v>5</v>
+      </c>
+      <c r="H60" s="14">
+        <v>70</v>
+      </c>
+      <c r="I60" s="15">
+        <f t="shared" si="2"/>
+        <v>855</v>
+      </c>
+      <c r="J60" s="15">
+        <f t="shared" si="3"/>
+        <v>585</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B61" s="14">
+        <v>390</v>
+      </c>
+      <c r="C61" s="14">
+        <v>20</v>
+      </c>
+      <c r="D61" s="14">
+        <v>50</v>
+      </c>
+      <c r="E61" s="14">
+        <v>40</v>
+      </c>
+      <c r="F61" s="14">
+        <v>250</v>
+      </c>
+      <c r="G61" s="14">
+        <v>5</v>
+      </c>
+      <c r="H61" s="14">
+        <v>190</v>
+      </c>
+      <c r="I61" s="15">
+        <f t="shared" si="2"/>
+        <v>940</v>
+      </c>
+      <c r="J61" s="15">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" s="16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B62" s="14">
+        <v>370</v>
+      </c>
+      <c r="C62" s="14">
+        <v>20</v>
+      </c>
+      <c r="D62" s="14">
+        <v>60</v>
+      </c>
+      <c r="E62" s="14">
+        <v>60</v>
+      </c>
+      <c r="F62" s="14">
+        <v>300</v>
+      </c>
+      <c r="G62" s="14">
+        <v>6</v>
+      </c>
+      <c r="H62" s="14">
+        <v>70</v>
+      </c>
+      <c r="I62" s="15">
+        <f t="shared" si="2"/>
+        <v>880</v>
+      </c>
+      <c r="J62" s="15">
+        <f t="shared" si="3"/>
+        <v>560</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N62" s="16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B63" s="14">
+        <v>380</v>
+      </c>
+      <c r="C63" s="14">
+        <v>25</v>
+      </c>
+      <c r="D63" s="14">
+        <v>50</v>
+      </c>
+      <c r="E63" s="14">
+        <v>35</v>
+      </c>
+      <c r="F63" s="14">
+        <v>350</v>
+      </c>
+      <c r="G63" s="14">
+        <v>7</v>
+      </c>
+      <c r="H63" s="14">
+        <v>260</v>
+      </c>
+      <c r="I63" s="15">
+        <f t="shared" si="2"/>
+        <v>1100</v>
+      </c>
+      <c r="J63" s="15">
+        <f t="shared" si="3"/>
+        <v>340</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N63" s="16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B64" s="14">
+        <v>450</v>
+      </c>
+      <c r="C64" s="14">
+        <v>15</v>
+      </c>
+      <c r="D64" s="14">
+        <v>190</v>
+      </c>
+      <c r="E64" s="14">
+        <v>20</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>240</v>
+      </c>
+      <c r="I64" s="15">
+        <f t="shared" si="2"/>
+        <v>915</v>
+      </c>
+      <c r="J64" s="15">
+        <f t="shared" si="3"/>
+        <v>525</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N64" s="16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B65" s="14">
+        <v>350</v>
+      </c>
+      <c r="C65" s="14">
+        <v>20</v>
+      </c>
+      <c r="D65" s="14">
+        <v>320</v>
+      </c>
+      <c r="E65" s="14">
+        <v>30</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>190</v>
+      </c>
+      <c r="I65" s="15">
+        <f t="shared" si="2"/>
+        <v>910</v>
+      </c>
+      <c r="J65" s="15">
+        <f t="shared" si="3"/>
+        <v>530</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N65" s="16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B66" s="14">
+        <v>390</v>
+      </c>
+      <c r="C66" s="14">
+        <v>10</v>
+      </c>
+      <c r="D66" s="14">
+        <v>240</v>
+      </c>
+      <c r="E66" s="14">
+        <v>20</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>35</v>
+      </c>
+      <c r="I66" s="15">
+        <f t="shared" si="2"/>
+        <v>695</v>
+      </c>
+      <c r="J66" s="15">
+        <f t="shared" si="3"/>
+        <v>745</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="16" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="8">
-        <v>46297</v>
-      </c>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="10" t="str">
+    <row r="67" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B67" s="14">
+        <v>410</v>
+      </c>
+      <c r="C67" s="14">
+        <v>15</v>
+      </c>
+      <c r="D67" s="14">
+        <v>270</v>
+      </c>
+      <c r="E67" s="14">
+        <v>40</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>40</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J56" s="10" t="str">
+        <v>775</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="12"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="10" t="str">
+        <v>665</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N67" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B68" s="14">
+        <v>390</v>
+      </c>
+      <c r="C68" s="14">
+        <v>20</v>
+      </c>
+      <c r="D68" s="14">
+        <v>220</v>
+      </c>
+      <c r="E68" s="14">
+        <v>45</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>55</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J57" s="10" t="str">
+        <v>730</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="12"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="10" t="str">
+        <v>710</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B69" s="14">
+        <v>450</v>
+      </c>
+      <c r="C69" s="14">
+        <v>30</v>
+      </c>
+      <c r="D69" s="14">
+        <v>320</v>
+      </c>
+      <c r="E69" s="14">
+        <v>30</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>20</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J58" s="10" t="str">
+        <v>850</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="12"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="12"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J60" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="12"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J61" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="12"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J62" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="12"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J63" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="12"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J64" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="12"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="12"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="12"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="12"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="12"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="12"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
+        <v>590</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N69" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B70" s="14">
+        <v>370</v>
+      </c>
+      <c r="C70" s="14">
+        <v>10</v>
+      </c>
+      <c r="D70" s="14">
+        <v>350</v>
+      </c>
+      <c r="E70" s="14">
+        <v>60</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>50</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
+        <v>840</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="12"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
+        <v>600</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B71" s="14">
+        <v>420</v>
+      </c>
+      <c r="C71" s="14">
+        <v>20</v>
+      </c>
+      <c r="D71" s="14">
+        <v>310</v>
+      </c>
+      <c r="E71" s="14">
+        <v>60</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>80</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
+        <v>890</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="12"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
+        <v>550</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N71" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B72" s="14">
+        <v>510</v>
+      </c>
+      <c r="C72" s="14">
+        <v>30</v>
+      </c>
+      <c r="D72" s="14">
+        <v>20</v>
+      </c>
+      <c r="E72" s="14">
+        <v>50</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>240</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+        <v>850</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="12"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
+        <v>590</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B73" s="14">
+        <v>390</v>
+      </c>
+      <c r="C73" s="14">
+        <v>20</v>
+      </c>
+      <c r="D73" s="14">
+        <v>50</v>
+      </c>
+      <c r="E73" s="14">
+        <v>60</v>
+      </c>
+      <c r="F73" s="14">
+        <v>200</v>
+      </c>
+      <c r="G73" s="14">
+        <v>4</v>
+      </c>
+      <c r="H73" s="14">
+        <v>60</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+        <v>780</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="12"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
+        <v>660</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B74" s="14">
+        <v>490</v>
+      </c>
+      <c r="C74" s="14">
+        <v>30</v>
+      </c>
+      <c r="D74" s="14">
+        <v>60</v>
+      </c>
+      <c r="E74" s="14">
+        <v>80</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>180</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+        <v>840</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="12"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
+        <v>600</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N74" s="16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B75" s="14">
+        <v>450</v>
+      </c>
+      <c r="C75" s="14">
+        <v>20</v>
+      </c>
+      <c r="D75" s="14">
+        <v>50</v>
+      </c>
+      <c r="E75" s="14">
+        <v>40</v>
+      </c>
+      <c r="F75" s="14">
+        <v>250</v>
+      </c>
+      <c r="G75" s="14">
+        <v>5</v>
+      </c>
+      <c r="H75" s="14">
+        <v>80</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+        <v>890</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="12"/>
+        <v>550</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N75" s="16" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>
